--- a/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
+++ b/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727C1377-427C-4D1F-B5C0-18B587D2FCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14CD923-DBDF-4099-9687-0CEAC240FDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>CONSORCIO DE COPROPIETARIOS PUEYRREDON 1494</t>
   </si>
   <si>
-    <t>VTO 14/07</t>
-  </si>
-  <si>
     <t>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS.</t>
   </si>
   <si>
@@ -462,30 +459,12 @@
     <t>Las expensas deberán abonarse en el Banco Comafi. Cuenta Corriente en pesos.                                                                                                                                                               Número 0240-00485/3 CUIT: 30-68041540-0 a nombre del Con. De Prop. C Pueyrredon 1494 - CBU 2990024602400048530006</t>
   </si>
   <si>
-    <t>PERÍODO: JUNIO</t>
-  </si>
-  <si>
-    <t>Mes de JUNIO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de JUNIO</t>
-  </si>
-  <si>
-    <t>Mantenimiento Ascensores - Mes de JUNIO</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>Tanque cuota 2 de 3 limpieza, recapeo, cambio de tapas</t>
-  </si>
-  <si>
     <t>Limpieza marquesina</t>
   </si>
   <si>
-    <t>Efect 12/06</t>
-  </si>
-  <si>
     <t>Debito 04/06</t>
   </si>
   <si>
@@ -498,9 +477,6 @@
     <t>PMC 10/06</t>
   </si>
   <si>
-    <t>Transf 11/06</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seguro de vida </t>
   </si>
   <si>
@@ -523,6 +499,30 @@
   </si>
   <si>
     <t>el mes pasado valeria hizo tres depositos (uno de 118mil, otro de 5mil y un ultimo de 10mil) de los cuales nosotros si bien se los pusimos, le escribimos mal el ultimo, en lugar de haberle puesto que hizo un deposito de 118mil, de 5mil y de 10 mil le pusimos de 118mil de 5mil y de mil, por lo que no debe tener deuda alguna, es mas, el mes anterior si le hubiesemos imputado bien los pagos le hubiesen quedado 171 pesos a favor)</t>
+  </si>
+  <si>
+    <t>Transf 17/07</t>
+  </si>
+  <si>
+    <t>VTO 14/08</t>
+  </si>
+  <si>
+    <t>PERÍODO: JULIO</t>
+  </si>
+  <si>
+    <t>Mes de JULIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JULIO</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de JULIO</t>
+  </si>
+  <si>
+    <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas</t>
+  </si>
+  <si>
+    <t>Efect 14/07</t>
   </si>
 </sst>
 </file>
@@ -530,14 +530,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="&quot;Bs&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1169,11 +1169,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1181,7 +1181,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1196,16 +1196,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -1217,8 +1217,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1228,25 +1228,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1254,11 +1254,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1272,8 +1272,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1281,18 +1281,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1303,129 +1303,139 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1435,21 +1445,14 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1758,27 +1761,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6"/>
       <c r="B1" s="32"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="76" t="s">
         <v>0</v>
@@ -1787,7 +1790,7 @@
       <c r="D2" s="76"/>
       <c r="E2" s="77"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="78" t="s">
         <v>1</v>
@@ -1796,7 +1799,7 @@
       <c r="D3" s="78"/>
       <c r="E3" s="79"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16"/>
       <c r="B4" s="93" t="s">
         <v>2</v>
@@ -1807,7 +1810,7 @@
       </c>
       <c r="E4" s="79"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
@@ -1818,12 +1821,12 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="78" t="s">
@@ -1831,7 +1834,7 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
@@ -1840,77 +1843,80 @@
       <c r="D7" s="20"/>
       <c r="E7" s="21"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="164" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="153" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="154"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="154"/>
+      <c r="C10" s="154"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="185"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="153"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="153"/>
-      <c r="C10" s="153"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="153"/>
-      <c r="C11" s="153"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="165" t="s">
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="153"/>
-      <c r="E14" s="153"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="153"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="153"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-      <c r="E16" s="153"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="153"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1919,9 +1925,9 @@
       </c>
       <c r="E23" s="96"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1930,9 +1936,9 @@
       </c>
       <c r="E24" s="96"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1942,7 +1948,7 @@
       <c r="E25" s="96"/>
       <c r="H25" s="22"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1950,9 +1956,9 @@
       <c r="E26" s="96"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="65"/>
       <c r="C27" s="65"/>
@@ -1963,9 +1969,9 @@
       <c r="E27" s="97"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1975,9 +1981,9 @@
       <c r="E28" s="96"/>
       <c r="H28" s="22"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1987,9 +1993,9 @@
       <c r="E29" s="96"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
@@ -1999,9 +2005,9 @@
       </c>
       <c r="E30" s="97"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -2012,34 +2018,34 @@
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" s="40"/>
       <c r="C32" s="40"/>
       <c r="D32" s="140"/>
       <c r="E32" s="99"/>
     </row>
-    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="186">
+        <v>35000</v>
+      </c>
+      <c r="E33" s="100"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="137">
-        <v>35000</v>
-      </c>
-      <c r="E33" s="100"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="B34" s="5" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="137">
@@ -2047,9 +2053,9 @@
       </c>
       <c r="E34" s="100"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -2059,18 +2065,18 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="39"/>
       <c r="C36" s="39"/>
       <c r="D36" s="142"/>
       <c r="E36" s="74"/>
     </row>
-    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="166" t="s">
-        <v>24</v>
+    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="158" t="s">
+        <v>23</v>
       </c>
       <c r="B37" s="156"/>
       <c r="C37" s="63"/>
@@ -2079,9 +2085,9 @@
       </c>
       <c r="E37" s="122"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="166" t="s">
-        <v>25</v>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="158" t="s">
+        <v>24</v>
       </c>
       <c r="B38" s="156"/>
       <c r="C38" s="63"/>
@@ -2090,9 +2096,9 @@
       </c>
       <c r="E38" s="122"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
@@ -2102,18 +2108,18 @@
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="145"/>
       <c r="E40" s="103"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="61"/>
@@ -2121,95 +2127,97 @@
         <v>371183.27</v>
       </c>
       <c r="E41" s="123" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G41" s="120"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="144">
-        <v>19236.05</v>
+      <c r="D42" s="184">
+        <v>32378.28</v>
       </c>
       <c r="E42" s="124" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
         <f>A42</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="144">
-        <v>62013.71</v>
+      <c r="D43" s="184">
+        <v>102414.9</v>
       </c>
       <c r="E43" s="124" t="str">
         <f>E42</f>
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de JUNIO</v>
+        <v>Sindicatos mes de JULIO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="144">
-        <v>3847.21</v>
+      <c r="D44" s="184">
+        <v>6475.66</v>
       </c>
       <c r="E44" s="125" t="str">
         <f>E43</f>
         <v>Debito 12/06</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="146"/>
       <c r="E45" s="102">
         <f>SUM(D41:D44)</f>
-        <v>456280.24000000005</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>512452.11000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="145"/>
       <c r="E46" s="103"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="61" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="144"/>
+      <c r="D47" s="184">
+        <v>36700</v>
+      </c>
       <c r="E47" s="106"/>
       <c r="G47" s="128" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2217,12 +2225,12 @@
         <v>69753.66</v>
       </c>
       <c r="E48" s="106" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2230,82 +2238,82 @@
         <v>25000</v>
       </c>
       <c r="E49" s="106" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G49" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="144">
-        <v>25000</v>
+      <c r="D50" s="184">
+        <v>30000</v>
       </c>
       <c r="E50" s="106" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="61" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="144">
+      <c r="D51" s="184">
         <v>1000000</v>
       </c>
       <c r="E51" s="106" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="155" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B52" s="156"/>
       <c r="C52" s="64"/>
-      <c r="D52" s="151">
-        <v>54750</v>
+      <c r="D52" s="183">
+        <v>67030</v>
       </c>
       <c r="E52" s="124" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="141"/>
       <c r="E53" s="102">
         <f>SUM(D47:D52)</f>
-        <v>1174503.6599999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1228483.6599999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="141"/>
       <c r="E54" s="105"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="61"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="42"/>
       <c r="E55" s="104"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" s="40"/>
       <c r="C56" s="40"/>
@@ -2315,18 +2323,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" s="73"/>
       <c r="C57" s="30"/>
       <c r="D57" s="139"/>
       <c r="E57" s="105"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2335,9 +2343,9 @@
       </c>
       <c r="E58" s="109"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2346,9 +2354,9 @@
       </c>
       <c r="E59" s="107"/>
     </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B60" s="60"/>
       <c r="C60" s="60"/>
@@ -2358,86 +2366,86 @@
         <v>106121.4</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="96"/>
       <c r="E61" s="111"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" s="33"/>
       <c r="C62" s="33"/>
       <c r="D62" s="112"/>
       <c r="E62" s="113"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1"/>
       <c r="D63" s="114"/>
       <c r="E63" s="115"/>
       <c r="F63" s="51"/>
     </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="10"/>
       <c r="C64" s="4"/>
       <c r="D64" s="116"/>
       <c r="E64" s="117">
         <f>(SUM(E31:E62))</f>
-        <v>3308689.9099999997</v>
+        <v>3418841.78</v>
       </c>
       <c r="F64" s="51"/>
       <c r="G64" s="128"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D65" s="114"/>
       <c r="E65" s="114"/>
       <c r="G65" s="128"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D66" s="114"/>
       <c r="E66" s="114"/>
     </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="13"/>
       <c r="D67" s="118"/>
       <c r="E67" s="119"/>
     </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="155" t="s">
-        <v>163</v>
-      </c>
-      <c r="B68" s="157"/>
+        <v>155</v>
+      </c>
+      <c r="B68" s="161"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="161">
+      <c r="D68" s="165">
         <v>181000</v>
       </c>
-      <c r="E68" s="163"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="158"/>
-      <c r="B69" s="159"/>
+      <c r="E68" s="167"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="162"/>
+      <c r="B69" s="163"/>
       <c r="C69" s="61"/>
-      <c r="D69" s="162"/>
-      <c r="E69" s="162"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D69" s="166"/>
+      <c r="E69" s="166"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="155"/>
       <c r="B70" s="156"/>
       <c r="C70" s="61"/>
       <c r="D70" s="42"/>
       <c r="E70" s="149"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="58"/>
       <c r="B71" s="57"/>
       <c r="C71" s="57"/>
@@ -2447,19 +2455,19 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B73" s="33"/>
       <c r="C73" s="33"/>
       <c r="D73" s="34"/>
       <c r="E73" s="129"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B75" s="10"/>
       <c r="C75" s="4"/>
@@ -2469,86 +2477,86 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" s="95">
         <f>E64</f>
-        <v>3308689.9099999997</v>
+        <v>3418841.78</v>
       </c>
       <c r="D77" s="51"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B78" s="95">
         <f>E64-E62</f>
-        <v>3308689.9099999997</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>3418841.78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B79" s="95">
         <f>E75-E73</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B80" s="95">
         <f>E75</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="152"/>
-      <c r="B83" s="153"/>
-      <c r="C83" s="153"/>
-      <c r="D83" s="153"/>
-      <c r="E83" s="153"/>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="153"/>
-      <c r="B84" s="153"/>
-      <c r="C84" s="153"/>
-      <c r="D84" s="153"/>
-      <c r="E84" s="153"/>
-    </row>
-    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="153"/>
-      <c r="B85" s="153"/>
-      <c r="C85" s="153"/>
-      <c r="D85" s="153"/>
-      <c r="E85" s="153"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="159"/>
+      <c r="B83" s="154"/>
+      <c r="C83" s="154"/>
+      <c r="D83" s="154"/>
+      <c r="E83" s="154"/>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="154"/>
+      <c r="B84" s="154"/>
+      <c r="C84" s="154"/>
+      <c r="D84" s="154"/>
+      <c r="E84" s="154"/>
+    </row>
+    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="154"/>
+      <c r="B85" s="154"/>
+      <c r="C85" s="154"/>
+      <c r="D85" s="154"/>
+      <c r="E85" s="154"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B87" s="46"/>
       <c r="C87" s="24"/>
     </row>
-    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" s="127">
         <v>-149600.7575000003</v>
       </c>
       <c r="C88" s="26"/>
     </row>
-    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B89" s="47">
         <f>PRORRATEO!H25</f>
@@ -2556,23 +2564,23 @@
       </c>
       <c r="C89" s="24"/>
     </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B90" s="55"/>
       <c r="C90" s="24"/>
     </row>
-    <row r="91" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="133" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B91" s="55"/>
       <c r="C91" s="24"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B92" s="107">
         <f>B111</f>
@@ -2580,19 +2588,19 @@
       </c>
       <c r="C92" s="24"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B93" s="55">
         <f>-B78</f>
-        <v>-3308689.9099999997</v>
+        <v>-3418841.78</v>
       </c>
       <c r="C93" s="24"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B94" s="55">
         <f>-(B79)</f>
@@ -2600,49 +2608,49 @@
       </c>
       <c r="C94" s="24"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B95" s="126">
         <f>SUM(B88:B94)</f>
-        <v>-1000157.7574999998</v>
+        <v>-1110309.6274999999</v>
       </c>
       <c r="C95" s="27"/>
     </row>
-    <row r="96" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="48"/>
       <c r="C96" s="27"/>
       <c r="D96" s="51"/>
     </row>
-    <row r="97" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="49"/>
       <c r="C97" s="27"/>
     </row>
-    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="48"/>
       <c r="C98" s="43"/>
     </row>
-    <row r="99" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B99" s="41"/>
       <c r="C99" s="43"/>
       <c r="D99" s="54"/>
     </row>
-    <row r="100" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B100" s="42">
         <v>0</v>
       </c>
       <c r="C100" s="43"/>
     </row>
-    <row r="101" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B101" s="41">
         <v>0</v>
@@ -2650,27 +2658,27 @@
       <c r="C101" s="27"/>
       <c r="D101" s="51"/>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B102" s="41">
         <v>0</v>
       </c>
       <c r="C102" s="27"/>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B103" s="41">
         <v>0</v>
       </c>
       <c r="C103" s="29"/>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B104" s="56">
         <f>SUM(B100:B103)</f>
@@ -2678,35 +2686,35 @@
       </c>
       <c r="C104" s="24"/>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="154" t="s">
-        <v>61</v>
-      </c>
-      <c r="B107" s="153"/>
-      <c r="C107" s="153"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="153"/>
-      <c r="B108" s="153"/>
-      <c r="C108" s="153"/>
-    </row>
-    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="160" t="s">
+        <v>60</v>
+      </c>
+      <c r="B107" s="154"/>
+      <c r="C107" s="154"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="154"/>
+      <c r="B108" s="154"/>
+      <c r="C108" s="154"/>
+    </row>
+    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="63"/>
       <c r="B109" s="41"/>
       <c r="C109" s="41">
         <v>40000</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="63"/>
       <c r="B110" s="41"/>
       <c r="C110" s="48"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B111" s="121">
         <f>SUM(B109:B110)</f>
@@ -2714,44 +2722,39 @@
       </c>
       <c r="C111" s="53"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M112" s="8"/>
     </row>
-    <row r="113" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="160"/>
-      <c r="B113" s="153"/>
-      <c r="C113" s="153"/>
-      <c r="D113" s="153"/>
-      <c r="E113" s="153"/>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="153"/>
-      <c r="B114" s="153"/>
-      <c r="C114" s="153"/>
-      <c r="D114" s="153"/>
-      <c r="E114" s="153"/>
-    </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="153"/>
-      <c r="B115" s="153"/>
-      <c r="C115" s="153"/>
-      <c r="D115" s="153"/>
-      <c r="E115" s="153"/>
-    </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="153"/>
-      <c r="B116" s="153"/>
-      <c r="C116" s="153"/>
-      <c r="D116" s="153"/>
-      <c r="E116" s="153"/>
+    <row r="113" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="164"/>
+      <c r="B113" s="154"/>
+      <c r="C113" s="154"/>
+      <c r="D113" s="154"/>
+      <c r="E113" s="154"/>
+    </row>
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="154"/>
+      <c r="B114" s="154"/>
+      <c r="C114" s="154"/>
+      <c r="D114" s="154"/>
+      <c r="E114" s="154"/>
+    </row>
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="154"/>
+      <c r="B115" s="154"/>
+      <c r="C115" s="154"/>
+      <c r="D115" s="154"/>
+      <c r="E115" s="154"/>
+    </row>
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="154"/>
+      <c r="B116" s="154"/>
+      <c r="C116" s="154"/>
+      <c r="D116" s="154"/>
+      <c r="E116" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A83:E85"/>
     <mergeCell ref="A107:C108"/>
     <mergeCell ref="A70:B70"/>
@@ -2759,6 +2762,11 @@
     <mergeCell ref="A113:E116"/>
     <mergeCell ref="D68:D69"/>
     <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2768,52 +2776,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="179" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2829,23 +2837,23 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="173">
+      <c r="O2" s="177">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="153"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -2855,106 +2863,106 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="177">
+      <c r="O3" s="181">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="178"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="167" t="s">
+      <c r="P3" s="182"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="175" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="174" t="s">
+      <c r="C4" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="D4" s="168" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="169" t="s">
+      <c r="E4" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="170" t="s">
+      <c r="F4" s="168" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="169" t="s">
+      <c r="G4" s="168" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="H4" s="168" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="169" t="s">
+      <c r="I4" s="170" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="170" t="s">
+      <c r="J4" s="173" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="180" t="s">
+      <c r="K4" s="176" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="172" t="s">
+      <c r="L4" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="181" t="s">
+      <c r="M4" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="172" t="s">
+      <c r="N4" s="176" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="172" t="s">
+      <c r="O4" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="69" t="s">
+      <c r="P4" s="180" t="s">
         <v>81</v>
-      </c>
-      <c r="P4" s="176" t="s">
-        <v>82</v>
       </c>
       <c r="S4" s="51"/>
       <c r="T4">
         <v>3000000</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="168"/>
-      <c r="B5" s="175"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="169"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="171"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
       <c r="I5" s="171"/>
       <c r="J5" s="171"/>
       <c r="K5" s="171"/>
-      <c r="L5" s="168"/>
+      <c r="L5" s="169"/>
       <c r="M5" s="171"/>
       <c r="N5" s="171"/>
       <c r="O5" s="67" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/07</v>
-      </c>
-      <c r="P5" s="168"/>
-    </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 14/08</v>
+      </c>
+      <c r="P5" s="169"/>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="70">
         <v>1</v>
       </c>
       <c r="C6" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="E6" s="70" t="s">
         <v>85</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>86</v>
       </c>
       <c r="F6" s="80">
         <v>3</v>
@@ -3003,21 +3011,21 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="70">
         <v>2</v>
       </c>
       <c r="C7" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="E7" s="70" t="s">
         <v>89</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>90</v>
       </c>
       <c r="F7" s="80">
         <v>3.8</v>
@@ -3063,21 +3071,21 @@
       </c>
       <c r="R7" s="51"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="70">
         <v>3</v>
       </c>
       <c r="C8" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="E8" s="70" t="s">
         <v>92</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>93</v>
       </c>
       <c r="F8" s="80">
         <v>3</v>
@@ -3123,21 +3131,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="70">
         <v>4</v>
       </c>
       <c r="C9" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="E9" s="70" t="s">
         <v>96</v>
-      </c>
-      <c r="E9" s="70" t="s">
-        <v>97</v>
       </c>
       <c r="F9" s="80">
         <v>3.1</v>
@@ -3183,21 +3191,21 @@
       </c>
       <c r="S9" s="51"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="70">
         <v>5</v>
       </c>
       <c r="C10" s="70" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="E10" s="70" t="s">
         <v>99</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>100</v>
       </c>
       <c r="F10" s="80">
         <v>3.1</v>
@@ -3244,18 +3252,18 @@
       </c>
       <c r="S10" s="51"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="70">
         <v>6</v>
       </c>
       <c r="C11" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="70" t="s">
         <v>102</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>103</v>
       </c>
       <c r="E11" s="70"/>
       <c r="F11" s="80">
@@ -3302,21 +3310,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="70">
         <v>7</v>
       </c>
       <c r="C12" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="E12" s="70" t="s">
         <v>105</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>106</v>
       </c>
       <c r="F12" s="80">
         <v>3.3</v>
@@ -3361,21 +3369,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" s="70">
         <v>23</v>
       </c>
       <c r="C13" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="E13" s="70" t="s">
         <v>109</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>110</v>
       </c>
       <c r="F13" s="80">
         <v>6.3</v>
@@ -3421,24 +3429,24 @@
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B14" s="70">
         <v>22</v>
       </c>
       <c r="C14" s="70" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="E14" s="70" t="s">
         <v>113</v>
-      </c>
-      <c r="E14" s="70" t="s">
-        <v>114</v>
       </c>
       <c r="F14" s="80">
         <v>5.0999999999999996</v>
@@ -3483,18 +3491,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="70">
         <v>21</v>
       </c>
       <c r="C15" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="70" t="s">
         <v>116</v>
-      </c>
-      <c r="D15" s="70" t="s">
-        <v>117</v>
       </c>
       <c r="E15" s="71"/>
       <c r="F15" s="80">
@@ -3540,21 +3548,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="70">
         <v>14</v>
       </c>
       <c r="C16" s="70" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="70" t="s">
+      <c r="E16" s="70" t="s">
         <v>119</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>120</v>
       </c>
       <c r="F16" s="80">
         <v>6.1</v>
@@ -3600,18 +3608,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="70">
         <v>13</v>
       </c>
       <c r="C17" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="70" t="s">
         <v>122</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>123</v>
       </c>
       <c r="E17" s="71"/>
       <c r="F17" s="80">
@@ -3657,21 +3665,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="70">
         <v>12</v>
       </c>
       <c r="C18" s="70" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="70" t="s">
+      <c r="E18" s="70" t="s">
         <v>125</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>126</v>
       </c>
       <c r="F18" s="80">
         <v>8.1999999999999993</v>
@@ -3716,18 +3724,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B19" s="70">
         <v>17</v>
       </c>
       <c r="C19" s="70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D19" s="70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E19" s="71"/>
       <c r="F19" s="80">
@@ -3771,29 +3779,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B20" s="70">
         <v>16</v>
       </c>
       <c r="C20" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="E20" s="71" t="s">
         <v>130</v>
-      </c>
-      <c r="E20" s="71" t="s">
-        <v>131</v>
       </c>
       <c r="F20" s="80">
         <v>5</v>
       </c>
-      <c r="G20" s="182">
+      <c r="G20" s="151">
         <v>132829.16</v>
       </c>
-      <c r="H20" s="182">
+      <c r="H20" s="151">
         <f>118000+5000+1000</f>
         <v>124000</v>
       </c>
@@ -3831,21 +3839,21 @@
         <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B21" s="70">
         <v>15</v>
       </c>
       <c r="C21" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="70" t="s">
         <v>133</v>
-      </c>
-      <c r="D21" s="70" t="s">
-        <v>134</v>
       </c>
       <c r="E21" s="70"/>
       <c r="F21" s="80">
@@ -3892,18 +3900,18 @@
       </c>
       <c r="S21" s="50"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B22" s="70">
         <v>20</v>
       </c>
       <c r="C22" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="70" t="s">
         <v>135</v>
-      </c>
-      <c r="D22" s="70" t="s">
-        <v>136</v>
       </c>
       <c r="E22" s="71"/>
       <c r="F22" s="80">
@@ -3950,21 +3958,21 @@
         <v>20</v>
       </c>
       <c r="T22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="B23" s="70">
         <v>19</v>
       </c>
       <c r="C23" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="70" t="s">
         <v>139</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>140</v>
       </c>
       <c r="E23" s="70"/>
       <c r="F23" s="80">
@@ -4011,18 +4019,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B24" s="70">
         <v>18</v>
       </c>
       <c r="C24" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="70" t="s">
         <v>141</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>142</v>
       </c>
       <c r="E24" s="71"/>
       <c r="F24" s="80">
@@ -4069,10 +4077,10 @@
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="86"/>
       <c r="C25" s="87"/>
       <c r="D25" s="88"/>
@@ -4119,112 +4127,105 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="59"/>
       <c r="E26" s="59"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="160" t="s">
-        <v>144</v>
-      </c>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="153"/>
-      <c r="L28" s="153"/>
-      <c r="M28" s="153"/>
-      <c r="N28" s="153"/>
-      <c r="O28" s="153"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="153"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="153"/>
-      <c r="L29" s="153"/>
-      <c r="M29" s="153"/>
-      <c r="N29" s="153"/>
-      <c r="O29" s="153"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="153"/>
-      <c r="M30" s="153"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="153"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="153"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="153"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="153"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="153"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="153"/>
-      <c r="I32" s="153"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="153"/>
-      <c r="L32" s="153"/>
-      <c r="M32" s="153"/>
-      <c r="N32" s="153"/>
-      <c r="O32" s="153"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="153"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="153"/>
-      <c r="I33" s="153"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="153"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="153"/>
-      <c r="N33" s="153"/>
-      <c r="O33" s="153"/>
-      <c r="R33" s="183" t="s">
-        <v>165</v>
-      </c>
-      <c r="S33" s="183"/>
-      <c r="T33" s="183"/>
-      <c r="U33" s="183"/>
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="164" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="154"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="154"/>
+      <c r="M32" s="154"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="154"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="154"/>
+      <c r="R33" s="152" t="s">
+        <v>157</v>
+      </c>
+      <c r="S33" s="152"/>
+      <c r="T33" s="152"/>
+      <c r="U33" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4237,6 +4238,13 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
+++ b/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14CD923-DBDF-4099-9687-0CEAC240FDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569747FC-6C2E-4E1A-939A-03002F9AAC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -468,12 +468,6 @@
     <t>Debito 04/06</t>
   </si>
   <si>
-    <t>Transf 30/06</t>
-  </si>
-  <si>
-    <t>Debito 12/06</t>
-  </si>
-  <si>
     <t>PMC 10/06</t>
   </si>
   <si>
@@ -489,9 +483,6 @@
     <t>METROGAS LO VENIMOS DIBUJANDO HACE 1 MES - HAY QUE ARREGLARLO</t>
   </si>
   <si>
-    <t>DEBEMOS MANTENIMIENTO DE ASCENSORES JUN</t>
-  </si>
-  <si>
     <t xml:space="preserve">4/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
   </si>
   <si>
@@ -519,10 +510,16 @@
     <t>Mantenimiento Ascensores - Mes de JULIO</t>
   </si>
   <si>
-    <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas</t>
-  </si>
-  <si>
     <t>Efect 14/07</t>
+  </si>
+  <si>
+    <t>Debito 14/07</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de JUNIO</t>
+  </si>
+  <si>
+    <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas - Se deben $500.000</t>
   </si>
 </sst>
 </file>
@@ -530,14 +527,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;Bs&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="&quot;Bs&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1169,11 +1166,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1181,7 +1178,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1196,16 +1193,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
@@ -1217,8 +1214,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1228,25 +1225,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1254,11 +1251,11 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1272,8 +1269,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1281,18 +1278,18 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1303,139 +1300,134 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="24" fillId="8" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1445,14 +1437,27 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1760,28 +1765,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="32"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="76" t="s">
         <v>0</v>
@@ -1790,7 +1795,7 @@
       <c r="D2" s="76"/>
       <c r="E2" s="77"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="78" t="s">
         <v>1</v>
@@ -1799,7 +1804,7 @@
       <c r="D3" s="78"/>
       <c r="E3" s="79"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
       <c r="B4" s="93" t="s">
         <v>2</v>
@@ -1810,7 +1815,7 @@
       </c>
       <c r="E4" s="79"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
@@ -1821,12 +1826,12 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="78" t="s">
@@ -1834,7 +1839,7 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>8</v>
       </c>
@@ -1843,60 +1848,60 @@
       <c r="D7" s="20"/>
       <c r="E7" s="21"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="153" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="154"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="185"/>
-    </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="157" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="169" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="158"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="158"/>
+      <c r="C11" s="158"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="155"/>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="154"/>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="154"/>
-      <c r="B15" s="154"/>
-      <c r="C15" s="154"/>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="154"/>
-      <c r="B16" s="154"/>
-      <c r="C16" s="154"/>
-      <c r="D16" s="154"/>
-      <c r="E16" s="154"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="154"/>
-      <c r="B17" s="154"/>
-      <c r="C17" s="154"/>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -1905,7 +1910,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="40" t="s">
         <v>11</v>
       </c>
@@ -1914,7 +1919,7 @@
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
@@ -1925,7 +1930,7 @@
       </c>
       <c r="E23" s="96"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
@@ -1936,7 +1941,7 @@
       </c>
       <c r="E24" s="96"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1948,7 +1953,7 @@
       <c r="E25" s="96"/>
       <c r="H25" s="22"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1956,7 +1961,7 @@
       <c r="E26" s="96"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="65" t="s">
         <v>15</v>
       </c>
@@ -1969,9 +1974,9 @@
       <c r="E27" s="97"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1981,9 +1986,9 @@
       <c r="E28" s="96"/>
       <c r="H28" s="22"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1993,7 +1998,7 @@
       <c r="E29" s="96"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>15</v>
       </c>
@@ -2005,7 +2010,7 @@
       </c>
       <c r="E30" s="97"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
         <v>16</v>
       </c>
@@ -2018,7 +2023,7 @@
       </c>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>17</v>
       </c>
@@ -2027,7 +2032,7 @@
       <c r="D32" s="140"/>
       <c r="E32" s="99"/>
     </row>
-    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="72" t="s">
         <v>18</v>
       </c>
@@ -2035,25 +2040,25 @@
         <v>20</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="186">
+      <c r="D33" s="156">
         <v>35000</v>
       </c>
       <c r="E33" s="100"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C34" s="5"/>
-      <c r="D34" s="137">
+      <c r="D34" s="156">
         <v>120000</v>
       </c>
       <c r="E34" s="100"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="30" t="s">
         <v>21</v>
       </c>
@@ -2065,7 +2070,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
         <v>22</v>
       </c>
@@ -2074,29 +2079,29 @@
       <c r="D36" s="142"/>
       <c r="E36" s="74"/>
     </row>
-    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="158" t="s">
+    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="171" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="156"/>
+      <c r="B37" s="161"/>
       <c r="C37" s="63"/>
       <c r="D37" s="143">
         <v>87562.7</v>
       </c>
       <c r="E37" s="122"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="158" t="s">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="171" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="156"/>
+      <c r="B38" s="161"/>
       <c r="C38" s="63"/>
       <c r="D38" s="144">
         <v>6646.91</v>
       </c>
       <c r="E38" s="122"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +2113,7 @@
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>26</v>
       </c>
@@ -2117,7 +2122,7 @@
       <c r="D40" s="145"/>
       <c r="E40" s="103"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
@@ -2127,26 +2132,26 @@
         <v>371183.27</v>
       </c>
       <c r="E41" s="123" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G41" s="120"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="184">
+      <c r="D42" s="154">
         <v>32378.28</v>
       </c>
       <c r="E42" s="124" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2155,15 +2160,15 @@
         <v>29</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="184">
+      <c r="D43" s="154">
         <v>102414.9</v>
       </c>
       <c r="E43" s="124" t="str">
         <f>E42</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2172,15 +2177,15 @@
         <v>30</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="184">
+      <c r="D44" s="154">
         <v>6475.66</v>
       </c>
       <c r="E44" s="125" t="str">
         <f>E43</f>
-        <v>Debito 12/06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 14/07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
         <v>31</v>
       </c>
@@ -2192,7 +2197,7 @@
         <v>512452.11000000004</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="40" t="s">
         <v>32</v>
       </c>
@@ -2201,572 +2206,581 @@
       <c r="D46" s="145"/>
       <c r="E46" s="103"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
         <v>163</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="184">
+      <c r="D47" s="154">
         <v>36700</v>
       </c>
       <c r="E47" s="106"/>
-      <c r="G47" s="128" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>33</v>
+      <c r="G47" s="128"/>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="61" t="s">
+        <v>160</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="144">
-        <v>69753.66</v>
-      </c>
-      <c r="E48" s="106" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D48" s="154">
+        <v>42500</v>
+      </c>
+      <c r="E48" s="106"/>
+      <c r="G48" s="128"/>
+    </row>
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="144">
-        <v>25000</v>
+        <v>69753.66</v>
       </c>
       <c r="E49" s="106" t="s">
-        <v>152</v>
-      </c>
-      <c r="G49" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="184">
-        <v>30000</v>
+      <c r="D50" s="144">
+        <v>25000</v>
       </c>
       <c r="E50" s="106" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="61" t="s">
-        <v>164</v>
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="184">
-        <v>1000000</v>
+      <c r="D51" s="154">
+        <v>30000</v>
       </c>
       <c r="E51" s="106" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="155" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="188" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="189"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="187">
+        <v>500000</v>
+      </c>
+      <c r="E52" s="106"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="160" t="s">
         <v>144</v>
       </c>
-      <c r="B52" s="156"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="183">
+      <c r="B53" s="161"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="153">
         <v>67030</v>
       </c>
-      <c r="E52" s="124" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="30" t="s">
+      <c r="E53" s="124" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="30" t="s">
         <v>35</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="102">
-        <f>SUM(D47:D52)</f>
-        <v>1228483.6599999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="40" t="s">
-        <v>36</v>
       </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="141"/>
-      <c r="E54" s="105"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="104"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="30" t="s">
+      <c r="E54" s="102">
+        <f>SUM(D47:D53)</f>
+        <v>770983.66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="105"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="61"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="104"/>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="108">
-        <f>SUM(D55:D55)</f>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="108">
+        <f>SUM(D56:D56)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="40" t="s">
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="139"/>
-      <c r="E57" s="105"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+      <c r="B58" s="73"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="139"/>
+      <c r="E58" s="105"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="144">
-        <v>57039.4</v>
-      </c>
-      <c r="E58" s="109"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="144">
+      <c r="D59" s="190">
+        <v>57039.4</v>
+      </c>
+      <c r="E59" s="109"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="190">
         <v>49082</v>
       </c>
-      <c r="E59" s="107"/>
-    </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="60" t="s">
+      <c r="E60" s="107"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="60"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="110"/>
-      <c r="E60" s="102">
-        <f>SUM(D58:D59)</f>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="102">
+        <f>SUM(D59:D60)</f>
         <v>106121.4</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="111"/>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="33" t="s">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="96"/>
+      <c r="E62" s="111"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
-      <c r="D62" s="112"/>
-      <c r="E62" s="113"/>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="1"/>
-      <c r="D63" s="114"/>
-      <c r="E63" s="115"/>
-      <c r="F63" s="51"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="112"/>
+      <c r="E63" s="113"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="D64" s="114"/>
+      <c r="E64" s="115"/>
+      <c r="F64" s="51"/>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B64" s="10"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="116"/>
-      <c r="E64" s="117">
-        <f>(SUM(E31:E62))</f>
-        <v>3418841.78</v>
-      </c>
-      <c r="F64" s="51"/>
-      <c r="G64" s="128"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D65" s="114"/>
-      <c r="E65" s="114"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="116"/>
+      <c r="E65" s="117">
+        <f>(SUM(E31:E63))</f>
+        <v>2961341.7800000003</v>
+      </c>
+      <c r="F65" s="51"/>
       <c r="G65" s="128"/>
     </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D66" s="114"/>
       <c r="E66" s="114"/>
-    </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+      <c r="G66" s="128"/>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="114"/>
+      <c r="E67" s="114"/>
+    </row>
+    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="119"/>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="155" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="161"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="165">
+      <c r="B68" s="12"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="118"/>
+      <c r="E68" s="119"/>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="160" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="162"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="166">
         <v>181000</v>
       </c>
-      <c r="E68" s="167"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="162"/>
-      <c r="B69" s="163"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="166"/>
-      <c r="E69" s="166"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="155"/>
-      <c r="B70" s="156"/>
+      <c r="E69" s="168"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="163"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="61"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="149"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="58"/>
-      <c r="B71" s="57"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="66">
-        <f>SUM(D68:D70)</f>
+      <c r="D70" s="167"/>
+      <c r="E70" s="167"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="160"/>
+      <c r="B71" s="161"/>
+      <c r="C71" s="61"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="149"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="58"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="57"/>
+      <c r="D72" s="66"/>
+      <c r="E72" s="66">
+        <f>SUM(D69:D71)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="33" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="129"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+      <c r="B74" s="33"/>
+      <c r="C74" s="33"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="129"/>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="75">
-        <f>E71+E73</f>
+      <c r="B76" s="10"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="75">
+        <f>E72+E74</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="94" t="s">
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="B77" s="95">
-        <f>E64</f>
-        <v>3418841.78</v>
-      </c>
-      <c r="D77" s="51"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="94" t="s">
+      <c r="B78" s="95">
+        <f>E65</f>
+        <v>2961341.7800000003</v>
+      </c>
+      <c r="D78" s="51"/>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="B78" s="95">
-        <f>E64-E62</f>
-        <v>3418841.78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="94" t="s">
+      <c r="B79" s="95">
+        <f>E65-E63</f>
+        <v>2961341.7800000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="B79" s="95">
-        <f>E75-E73</f>
+      <c r="B80" s="95">
+        <f>E76-E74</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="94" t="s">
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="95">
-        <f>E75</f>
+      <c r="B81" s="95">
+        <f>E76</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="159"/>
-      <c r="B83" s="154"/>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
-      <c r="E83" s="154"/>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="154"/>
-      <c r="B84" s="154"/>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
-      <c r="E84" s="154"/>
-    </row>
-    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="154"/>
-      <c r="B85" s="154"/>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
-      <c r="E85" s="154"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="23" t="s">
+    <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="157"/>
+      <c r="B84" s="158"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="158"/>
+      <c r="B85" s="158"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+    </row>
+    <row r="86" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="158"/>
+      <c r="B86" s="158"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B87" s="46"/>
-      <c r="C87" s="24"/>
-    </row>
-    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="36" t="s">
+      <c r="B88" s="46"/>
+      <c r="C88" s="24"/>
+    </row>
+    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B88" s="127">
+      <c r="B89" s="127">
         <v>-149600.7575000003</v>
       </c>
-      <c r="C88" s="26"/>
-    </row>
-    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="25" t="s">
+      <c r="C89" s="26"/>
+    </row>
+    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B89" s="47">
+      <c r="B90" s="47">
         <f>PRORRATEO!H25</f>
         <v>2639132.91</v>
       </c>
-      <c r="C89" s="24"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="25" t="s">
+      <c r="C90" s="24"/>
+    </row>
+    <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="B90" s="55"/>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="133" t="s">
-        <v>53</v>
       </c>
       <c r="B91" s="55"/>
       <c r="C91" s="24"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="25" t="s">
+    <row r="92" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="133" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" s="55"/>
+      <c r="C92" s="24"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B92" s="107">
-        <f>B111</f>
+      <c r="B93" s="107">
+        <f>B112</f>
         <v>0</v>
       </c>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="45" t="s">
+      <c r="C93" s="24"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B93" s="55">
-        <f>-B78</f>
-        <v>-3418841.78</v>
-      </c>
-      <c r="C93" s="24"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="28" t="s">
+      <c r="B94" s="55">
+        <f>-B79</f>
+        <v>-2961341.7800000003</v>
+      </c>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B94" s="55">
-        <f>-(B79)</f>
+      <c r="B95" s="55">
+        <f>-(B80)</f>
         <v>-181000</v>
       </c>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="35" t="s">
+      <c r="C95" s="24"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B95" s="126">
-        <f>SUM(B88:B94)</f>
-        <v>-1110309.6274999999</v>
-      </c>
-      <c r="C95" s="27"/>
-    </row>
-    <row r="96" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="48"/>
+      <c r="B96" s="126">
+        <f>SUM(B89:B95)</f>
+        <v>-652809.62750000041</v>
+      </c>
       <c r="C96" s="27"/>
-      <c r="D96" s="51"/>
-    </row>
-    <row r="97" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="49"/>
+    </row>
+    <row r="97" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="48"/>
       <c r="C97" s="27"/>
-    </row>
-    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="48"/>
-      <c r="C98" s="43"/>
-    </row>
-    <row r="99" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="37" t="s">
+      <c r="D97" s="51"/>
+    </row>
+    <row r="98" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="49"/>
+      <c r="C98" s="27"/>
+    </row>
+    <row r="99" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="48"/>
+      <c r="C99" s="43"/>
+    </row>
+    <row r="100" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="B99" s="41"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="54"/>
-    </row>
-    <row r="100" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
+      <c r="B100" s="41"/>
+      <c r="C100" s="43"/>
+      <c r="D100" s="54"/>
+    </row>
+    <row r="101" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B100" s="42">
+      <c r="B101" s="42">
         <v>0</v>
       </c>
-      <c r="C100" s="43"/>
-    </row>
-    <row r="101" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
+      <c r="C101" s="43"/>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B101" s="41">
-        <v>0</v>
-      </c>
-      <c r="C101" s="27"/>
-      <c r="D101" s="51"/>
-    </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="B102" s="41">
         <v>0</v>
       </c>
       <c r="C102" s="27"/>
-    </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D102" s="51"/>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B103" s="41">
         <v>0</v>
       </c>
-      <c r="C103" s="29"/>
-    </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="37" t="s">
+      <c r="C103" s="27"/>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B104" s="41">
+        <v>0</v>
+      </c>
+      <c r="C104" s="29"/>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B104" s="56">
-        <f>SUM(B100:B103)</f>
+      <c r="B105" s="56">
+        <f>SUM(B101:B104)</f>
         <v>0</v>
       </c>
-      <c r="C104" s="24"/>
-    </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="106" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="160" t="s">
+      <c r="C105" s="24"/>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="159" t="s">
         <v>60</v>
       </c>
-      <c r="B107" s="154"/>
-      <c r="C107" s="154"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A108" s="154"/>
-      <c r="B108" s="154"/>
-      <c r="C108" s="154"/>
-    </row>
-    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="63"/>
-      <c r="B109" s="41"/>
-      <c r="C109" s="41">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="158"/>
+      <c r="C108" s="158"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="158"/>
+      <c r="B109" s="158"/>
+      <c r="C109" s="158"/>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="63"/>
       <c r="B110" s="41"/>
-      <c r="C110" s="48"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A111" s="52" t="s">
+      <c r="C110" s="41">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="63"/>
+      <c r="B111" s="41"/>
+      <c r="C111" s="48"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B111" s="121">
-        <f>SUM(B109:B110)</f>
+      <c r="B112" s="121">
+        <f>SUM(B110:B111)</f>
         <v>0</v>
       </c>
-      <c r="C111" s="53"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M112" s="8"/>
-    </row>
-    <row r="113" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="164"/>
-      <c r="B113" s="154"/>
-      <c r="C113" s="154"/>
-      <c r="D113" s="154"/>
-      <c r="E113" s="154"/>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="154"/>
-      <c r="B114" s="154"/>
-      <c r="C114" s="154"/>
-      <c r="D114" s="154"/>
-      <c r="E114" s="154"/>
-    </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="154"/>
-      <c r="B115" s="154"/>
-      <c r="C115" s="154"/>
-      <c r="D115" s="154"/>
-      <c r="E115" s="154"/>
-    </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="154"/>
-      <c r="B116" s="154"/>
-      <c r="C116" s="154"/>
-      <c r="D116" s="154"/>
-      <c r="E116" s="154"/>
+      <c r="C112" s="53"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M113" s="8"/>
+    </row>
+    <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="165"/>
+      <c r="B114" s="158"/>
+      <c r="C114" s="158"/>
+      <c r="D114" s="158"/>
+      <c r="E114" s="158"/>
+    </row>
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="158"/>
+      <c r="B115" s="158"/>
+      <c r="C115" s="158"/>
+      <c r="D115" s="158"/>
+      <c r="E115" s="158"/>
+    </row>
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="158"/>
+      <c r="B116" s="158"/>
+      <c r="C116" s="158"/>
+      <c r="D116" s="158"/>
+      <c r="E116" s="158"/>
+    </row>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="158"/>
+      <c r="B117" s="158"/>
+      <c r="C117" s="158"/>
+      <c r="D117" s="158"/>
+      <c r="E117" s="158"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A83:E85"/>
-    <mergeCell ref="A107:C108"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A68:B69"/>
-    <mergeCell ref="A113:E116"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
+  <mergeCells count="13">
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A84:E86"/>
+    <mergeCell ref="A108:C109"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A69:B70"/>
+    <mergeCell ref="A114:E117"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2776,30 +2790,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2807,21 +2821,21 @@
         <v>61</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="172" t="s">
+      <c r="F1" s="184" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="154"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2841,14 +2855,14 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="177">
+      <c r="O2" s="178">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="154"/>
+      <c r="P2" s="158"/>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2867,59 +2881,59 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="181">
+      <c r="O3" s="182">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="182"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="175" t="s">
+      <c r="P3" s="183"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="179" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="174" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="174" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="170" t="s">
+      <c r="E4" s="175" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="168" t="s">
+      <c r="F4" s="174" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="168" t="s">
+      <c r="H4" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="170" t="s">
+      <c r="I4" s="175" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="173" t="s">
+      <c r="J4" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="L4" s="174" t="s">
+      <c r="L4" s="186" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="177" t="s">
         <v>78</v>
       </c>
-      <c r="N4" s="176" t="s">
+      <c r="N4" s="177" t="s">
         <v>79</v>
       </c>
       <c r="O4" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="180" t="s">
+      <c r="P4" s="181" t="s">
         <v>81</v>
       </c>
       <c r="S4" s="51"/>
@@ -2927,28 +2941,28 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="169"/>
-      <c r="B5" s="179"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="171"/>
-      <c r="J5" s="171"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="171"/>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="173"/>
+      <c r="B5" s="180"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="173"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
       <c r="O5" s="67" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="169"/>
-    </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="173"/>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>82</v>
       </c>
@@ -3011,7 +3025,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>86</v>
       </c>
@@ -3071,7 +3085,7 @@
       </c>
       <c r="R7" s="51"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>86</v>
       </c>
@@ -3131,7 +3145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>93</v>
       </c>
@@ -3191,7 +3205,7 @@
       </c>
       <c r="S9" s="51"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>93</v>
       </c>
@@ -3252,7 +3266,7 @@
       </c>
       <c r="S10" s="51"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>100</v>
       </c>
@@ -3310,7 +3324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>100</v>
       </c>
@@ -3369,7 +3383,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>106</v>
       </c>
@@ -3432,7 +3446,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>106</v>
       </c>
@@ -3491,7 +3505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>114</v>
       </c>
@@ -3548,7 +3562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>114</v>
       </c>
@@ -3608,7 +3622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>120</v>
       </c>
@@ -3665,7 +3679,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>120</v>
       </c>
@@ -3724,7 +3738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>126</v>
       </c>
@@ -3779,7 +3793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>126</v>
       </c>
@@ -3839,10 +3853,10 @@
         <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>131</v>
       </c>
@@ -3900,7 +3914,7 @@
       </c>
       <c r="S21" s="50"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>131</v>
       </c>
@@ -3961,7 +3975,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>137</v>
       </c>
@@ -4019,7 +4033,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>137</v>
       </c>
@@ -4080,7 +4094,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="86"/>
       <c r="C25" s="87"/>
       <c r="D25" s="88"/>
@@ -4127,98 +4141,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="59"/>
       <c r="E26" s="59"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="164" t="s">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="165" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="154"/>
-      <c r="J28" s="154"/>
-      <c r="K28" s="154"/>
-      <c r="L28" s="154"/>
-      <c r="M28" s="154"/>
-      <c r="N28" s="154"/>
-      <c r="O28" s="154"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="154"/>
-      <c r="N29" s="154"/>
-      <c r="O29" s="154"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D30" s="154"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="154"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="154"/>
-      <c r="I30" s="154"/>
-      <c r="J30" s="154"/>
-      <c r="K30" s="154"/>
-      <c r="L30" s="154"/>
-      <c r="M30" s="154"/>
-      <c r="N30" s="154"/>
-      <c r="O30" s="154"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="154"/>
-      <c r="J31" s="154"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="154"/>
-      <c r="M31" s="154"/>
-      <c r="N31" s="154"/>
-      <c r="O31" s="154"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="154"/>
-      <c r="I32" s="154"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="154"/>
-      <c r="L32" s="154"/>
-      <c r="M32" s="154"/>
-      <c r="N32" s="154"/>
-      <c r="O32" s="154"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D33" s="154"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="154"/>
-      <c r="I33" s="154"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="154"/>
-      <c r="O33" s="154"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="158"/>
+      <c r="M28" s="158"/>
+      <c r="N28" s="158"/>
+      <c r="O28" s="158"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="158"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="158"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="158"/>
+      <c r="L29" s="158"/>
+      <c r="M29" s="158"/>
+      <c r="N29" s="158"/>
+      <c r="O29" s="158"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
+      <c r="N30" s="158"/>
+      <c r="O30" s="158"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="158"/>
+      <c r="O31" s="158"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="158"/>
+      <c r="E32" s="158"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="158"/>
+      <c r="H32" s="158"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="158"/>
+      <c r="M32" s="158"/>
+      <c r="N32" s="158"/>
+      <c r="O32" s="158"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="158"/>
+      <c r="E33" s="158"/>
+      <c r="F33" s="158"/>
+      <c r="G33" s="158"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="158"/>
+      <c r="J33" s="158"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="158"/>
+      <c r="M33" s="158"/>
+      <c r="N33" s="158"/>
+      <c r="O33" s="158"/>
       <c r="R33" s="152" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="S33" s="152"/>
       <c r="T33" s="152"/>
@@ -4226,6 +4240,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4238,13 +4259,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
+++ b/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569747FC-6C2E-4E1A-939A-03002F9AAC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7100A170-7E8F-4AE5-A09C-997CB59F99F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$116</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Depisitos ya identificados</t>
   </si>
   <si>
-    <t>Punitorios mal cobrados de depositos identificados</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deposito sin identificar </t>
   </si>
   <si>
@@ -465,33 +462,12 @@
     <t>Limpieza marquesina</t>
   </si>
   <si>
-    <t>Debito 04/06</t>
-  </si>
-  <si>
-    <t>PMC 10/06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seguro de vida </t>
-  </si>
-  <si>
-    <t>Reemplazo Vacaciones Mirtha - Sra. Gisela</t>
-  </si>
-  <si>
-    <t>PMC 07/06</t>
-  </si>
-  <si>
     <t>METROGAS LO VENIMOS DIBUJANDO HACE 1 MES - HAY QUE ARREGLARLO</t>
   </si>
   <si>
-    <t xml:space="preserve">4/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
-  </si>
-  <si>
     <t>DEPOSITA SIEMPRE VALERIA</t>
   </si>
   <si>
-    <t>el mes pasado valeria hizo tres depositos (uno de 118mil, otro de 5mil y un ultimo de 10mil) de los cuales nosotros si bien se los pusimos, le escribimos mal el ultimo, en lugar de haberle puesto que hizo un deposito de 118mil, de 5mil y de 10 mil le pusimos de 118mil de 5mil y de mil, por lo que no debe tener deuda alguna, es mas, el mes anterior si le hubiesemos imputado bien los pagos le hubiesen quedado 171 pesos a favor)</t>
-  </si>
-  <si>
     <t>Transf 17/07</t>
   </si>
   <si>
@@ -520,6 +496,45 @@
   </si>
   <si>
     <t>Tanque cuota 3 de 3 limpieza, recapeo, cambio de tapas - Se deben $500.000</t>
+  </si>
+  <si>
+    <t>SUBIDOS EN JULI</t>
+  </si>
+  <si>
+    <t>PMC 28/07</t>
+  </si>
+  <si>
+    <t>PMC 12/07</t>
+  </si>
+  <si>
+    <t>Transf 28/07</t>
+  </si>
+  <si>
+    <t>Debito 30/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaffalon Veronica - Cambio de valvulas y adaptacion de cañeria bomba 1  </t>
+  </si>
+  <si>
+    <t>Transf 30/07</t>
+  </si>
+  <si>
+    <t>Servisur - cambio de luminarias (plafones, portalamparas, tubos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricidad Leon - Materiales </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punitorios mal cobrados </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
+  </si>
+  <si>
+    <t>Lourdes</t>
+  </si>
+  <si>
+    <t>11/07 Transf no identificada - Valentina Cecilia Zarate</t>
   </si>
 </sst>
 </file>
@@ -734,7 +749,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,14 +816,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="30">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1158,6 +1167,44 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1170,7 +1217,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1186,13 +1233,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1205,7 +1245,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1271,14 +1310,9 @@
     </xf>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1290,15 +1324,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1346,9 +1371,6 @@
     <xf numFmtId="168" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="23" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1368,29 +1390,38 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1404,26 +1435,26 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1441,23 +1472,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1476,6 +1524,54 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2238375" cy="847725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image1.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{383B74D3-69A2-44AC-93CA-6EA72C609EE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="104775" y="47625"/>
+          <a:ext cx="2238375" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1765,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1779,122 +1875,122 @@
     <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="175"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="178"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="76" t="s">
+      <c r="A2" s="179"/>
+      <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="77"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="180"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="78" t="s">
+      <c r="A3" s="179"/>
+      <c r="B3" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="79"/>
-    </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="93" t="s">
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="180"/>
+    </row>
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="179"/>
+      <c r="B4" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="92" t="s">
+      <c r="C4" s="171"/>
+      <c r="D4" s="173" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="79"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="E4" s="180"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="174" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="181"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="78" t="s">
+      <c r="B6" s="170" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="170"/>
+      <c r="D6" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="E6" s="181"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
+      <c r="B7" s="183"/>
+      <c r="C7" s="183"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="184"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="169" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="158"/>
+      <c r="B9" s="134" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="135"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="155"/>
+      <c r="B12" s="133"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="170" t="s">
+      <c r="A14" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="158"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
+      <c r="A16" s="135"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
+      <c r="A17" s="135"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -1911,13 +2007,13 @@
       <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1925,10 +2021,10 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="137">
-        <v>1292761.2</v>
-      </c>
-      <c r="E23" s="96"/>
+      <c r="D23" s="120">
+        <v>612874.4</v>
+      </c>
+      <c r="E23" s="80"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -1936,10 +2032,10 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="137">
-        <v>-281175.56</v>
-      </c>
-      <c r="E24" s="96"/>
+      <c r="D24" s="120">
+        <v>-143013.39000000001</v>
+      </c>
+      <c r="E24" s="80"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -1947,211 +2043,206 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="137">
-        <v>0.36</v>
-      </c>
-      <c r="E25" s="96"/>
-      <c r="H25" s="22"/>
+      <c r="D25" s="120">
+        <v>0.99</v>
+      </c>
+      <c r="E25" s="80"/>
+      <c r="H25" s="15"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="137"/>
-      <c r="E26" s="96"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="80"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="138">
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="121">
         <f>SUM(D23:D26)</f>
-        <v>1011585.9999999999</v>
-      </c>
-      <c r="E27" s="97"/>
+        <v>469862</v>
+      </c>
+      <c r="E27" s="81"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>149</v>
-      </c>
+    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="137">
-        <v>300000</v>
-      </c>
-      <c r="E28" s="96"/>
-      <c r="H28" s="22"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="D28" s="120"/>
+      <c r="E28" s="80"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="137">
-        <v>10989</v>
-      </c>
-      <c r="E29" s="96"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="80"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="150">
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="132">
         <f>SUM(D28:D29)</f>
-        <v>310989</v>
-      </c>
-      <c r="E30" s="97"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="81"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="98">
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="82">
         <f>D27+D30</f>
-        <v>1322575</v>
-      </c>
-      <c r="F31" s="22"/>
+        <v>469862</v>
+      </c>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="99"/>
-    </row>
-    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="72" t="s">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="83"/>
+    </row>
+    <row r="33" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="156">
+      <c r="D33" s="120">
         <v>35000</v>
       </c>
-      <c r="E33" s="100"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="84"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C34" s="5"/>
-      <c r="D34" s="156">
-        <v>120000</v>
-      </c>
-      <c r="E34" s="100"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="D34" s="120">
+        <v>135100</v>
+      </c>
+      <c r="E34" s="84"/>
+      <c r="H34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="141"/>
-      <c r="E35" s="101">
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="85">
         <f>SUM(D33:D34)</f>
-        <v>155000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="38" t="s">
+        <v>170100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="142"/>
-      <c r="E36" s="74"/>
-    </row>
-    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="171" t="s">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="66"/>
+    </row>
+    <row r="37" spans="1:8" s="36" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="161"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="143">
+      <c r="B37" s="137"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="126">
         <v>87562.7</v>
       </c>
-      <c r="E37" s="122"/>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="171" t="s">
+      <c r="E37" s="106"/>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="139" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="161"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="144">
+      <c r="B38" s="137"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="127">
         <v>6646.91</v>
       </c>
-      <c r="E38" s="122"/>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
+      <c r="E38" s="106"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="141"/>
-      <c r="E39" s="102">
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="86">
         <f>SUM(D37:D38)</f>
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="145"/>
-      <c r="E40" s="103"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="128"/>
+      <c r="E40" s="87"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="144">
-        <v>371183.27</v>
-      </c>
-      <c r="E41" s="123" t="s">
-        <v>147</v>
-      </c>
-      <c r="G41" s="120"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="53"/>
+      <c r="D41" s="127">
+        <v>620508.89</v>
+      </c>
+      <c r="E41" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" s="104"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="154">
+      <c r="D42" s="127">
         <v>32378.28</v>
       </c>
-      <c r="E42" s="124" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E42" s="108" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2160,15 +2251,15 @@
         <v>29</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="154">
+      <c r="D43" s="127">
         <v>102414.9</v>
       </c>
-      <c r="E43" s="124" t="str">
+      <c r="E43" s="108" t="str">
         <f>E42</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JULIO</v>
@@ -2177,58 +2268,62 @@
         <v>30</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="154">
+      <c r="D44" s="127">
         <v>6475.66</v>
       </c>
-      <c r="E44" s="125" t="str">
+      <c r="E44" s="109" t="str">
         <f>E43</f>
         <v>Debito 14/07</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="30" t="s">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="102">
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="129"/>
+      <c r="E45" s="86">
         <f>SUM(D41:D44)</f>
-        <v>512452.11000000004</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
+        <v>761777.7300000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="145"/>
-      <c r="E46" s="103"/>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="61" t="s">
-        <v>163</v>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="128"/>
+      <c r="E46" s="87"/>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="53" t="s">
+        <v>155</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="154">
+      <c r="D47" s="127">
         <v>36700</v>
       </c>
-      <c r="E47" s="106"/>
-      <c r="G47" s="128"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61" t="s">
+      <c r="E47" s="90" t="s">
         <v>160</v>
+      </c>
+      <c r="G47" s="112"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="53" t="s">
+        <v>152</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="154">
+      <c r="D48" s="127">
         <v>42500</v>
       </c>
-      <c r="E48" s="106"/>
-      <c r="G48" s="128"/>
+      <c r="E48" s="90" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" s="112"/>
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2236,11 +2331,11 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="144">
-        <v>69753.66</v>
-      </c>
-      <c r="E49" s="106" t="s">
-        <v>146</v>
+      <c r="D49" s="127">
+        <v>86610.08</v>
+      </c>
+      <c r="E49" s="90" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2249,541 +2344,590 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="144">
+      <c r="D50" s="127">
         <v>25000</v>
       </c>
-      <c r="E50" s="106" t="s">
-        <v>150</v>
+      <c r="E50" s="90" t="s">
+        <v>158</v>
       </c>
       <c r="G50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B51" s="5"/>
+    </row>
+    <row r="51" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="166" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="167"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="154">
+      <c r="D51" s="127">
+        <v>135000</v>
+      </c>
+      <c r="E51" s="90" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="127">
+        <v>119000</v>
+      </c>
+      <c r="E52" s="90" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="127">
+        <v>35626.879999999997</v>
+      </c>
+      <c r="E53" s="90" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="127">
         <v>30000</v>
       </c>
-      <c r="E51" s="106" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="188" t="s">
-        <v>164</v>
-      </c>
-      <c r="B52" s="189"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="187">
+      <c r="E54" s="90" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="140" t="s">
+        <v>156</v>
+      </c>
+      <c r="B55" s="141"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="127">
         <v>500000</v>
       </c>
-      <c r="E52" s="106"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="160" t="s">
-        <v>144</v>
-      </c>
-      <c r="B53" s="161"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="153">
+      <c r="E55" s="90"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="136" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="137"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="187">
         <v>67030</v>
       </c>
-      <c r="E53" s="124" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="30" t="s">
+      <c r="E56" s="108" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="141"/>
-      <c r="E54" s="102">
-        <f>SUM(D47:D53)</f>
-        <v>770983.66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="40" t="s">
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="86">
+        <f>SUM(D47:D56)</f>
+        <v>1077466.96</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="141"/>
-      <c r="E55" s="105"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="61"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="104"/>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="108">
-        <f>SUM(D56:D56)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="73"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="139"/>
-      <c r="E58" s="105"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="124"/>
+      <c r="E58" s="89"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="A59" s="53"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="190">
-        <v>57039.4</v>
-      </c>
-      <c r="E59" s="109"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="190">
-        <v>49082</v>
-      </c>
-      <c r="E60" s="107"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="88"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="92">
+        <f>SUM(D59:D59)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="B61" s="60"/>
-      <c r="C61" s="60"/>
-      <c r="D61" s="110"/>
-      <c r="E61" s="102">
-        <f>SUM(D59:D60)</f>
-        <v>106121.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
+      <c r="A61" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="65"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="122"/>
+      <c r="E61" s="89"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="96"/>
-      <c r="E62" s="111"/>
-    </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="33" t="s">
+      <c r="D62" s="127">
+        <v>48482.26</v>
+      </c>
+      <c r="E62" s="93"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="127">
+        <v>49082</v>
+      </c>
+      <c r="E63" s="91"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="94"/>
+      <c r="E64" s="86">
+        <f>SUM(D62:D63)</f>
+        <v>97564.260000000009</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="80"/>
+      <c r="E65" s="95"/>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="112"/>
-      <c r="E63" s="113"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="D64" s="114"/>
-      <c r="E64" s="115"/>
-      <c r="F64" s="51"/>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="96"/>
+      <c r="E66" s="97">
+        <v>529019.43999999994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="D67" s="98"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="43"/>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="116"/>
-      <c r="E65" s="117">
-        <f>(SUM(E31:E63))</f>
-        <v>2961341.7800000003</v>
-      </c>
-      <c r="F65" s="51"/>
-      <c r="G65" s="128"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D66" s="114"/>
-      <c r="E66" s="114"/>
-      <c r="G66" s="128"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="114"/>
-      <c r="E67" s="114"/>
-    </row>
-    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="B68" s="10"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="100"/>
+      <c r="E68" s="101">
+        <f>(SUM(E31:E66))</f>
+        <v>3199999.9999999995</v>
+      </c>
+      <c r="F68" s="43"/>
+      <c r="G68" s="112"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D69" s="98"/>
+      <c r="E69" s="98"/>
+      <c r="G69" s="112"/>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="98"/>
+      <c r="E70" s="98"/>
+    </row>
+    <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="119"/>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="160" t="s">
-        <v>152</v>
-      </c>
-      <c r="B69" s="162"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="166">
+      <c r="B71" s="12"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="102"/>
+      <c r="E71" s="103"/>
+    </row>
+    <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="136" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" s="144"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="148">
         <v>181000</v>
       </c>
-      <c r="E69" s="168"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="163"/>
-      <c r="B70" s="164"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="167"/>
-      <c r="E70" s="167"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="160"/>
-      <c r="B71" s="161"/>
-      <c r="C71" s="61"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="149"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="58"/>
-      <c r="B72" s="57"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="66"/>
-      <c r="E72" s="66">
-        <f>SUM(D69:D71)</f>
+      <c r="E72" s="150"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="145"/>
+      <c r="B73" s="146"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="186"/>
+      <c r="E73" s="149"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="136"/>
+      <c r="B74" s="137"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="131"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="50"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58">
+        <f>SUM(D72:D74)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="33" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B74" s="33"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="129"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="113"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="75">
-        <f>E72+E74</f>
+      <c r="B79" s="10"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="67">
+        <f>E75+E77</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="94" t="s">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="B78" s="95">
-        <f>E65</f>
-        <v>2961341.7800000003</v>
-      </c>
-      <c r="D78" s="51"/>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="94" t="s">
+      <c r="B81" s="79">
+        <f>E68</f>
+        <v>3199999.9999999995</v>
+      </c>
+      <c r="D81" s="43"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="B79" s="95">
-        <f>E65-E63</f>
-        <v>2961341.7800000003</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="94" t="s">
+      <c r="B82" s="79">
+        <f>E68-E66</f>
+        <v>2670980.5599999996</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="95">
-        <f>E76-E74</f>
+      <c r="B83" s="79">
+        <f>E79-E77</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="94" t="s">
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="B81" s="95">
-        <f>E76</f>
+      <c r="B84" s="79">
+        <f>E79</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="157"/>
-      <c r="B84" s="158"/>
-      <c r="C84" s="158"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-    </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="158"/>
-      <c r="B85" s="158"/>
-      <c r="C85" s="158"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-    </row>
-    <row r="86" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="158"/>
-      <c r="B86" s="158"/>
-      <c r="C86" s="158"/>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="23" t="s">
+    <row r="85" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="142"/>
+      <c r="B87" s="135"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="135"/>
+      <c r="E87" s="135"/>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="135"/>
+      <c r="B88" s="135"/>
+      <c r="C88" s="135"/>
+      <c r="D88" s="135"/>
+      <c r="E88" s="135"/>
+    </row>
+    <row r="89" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="135"/>
+      <c r="B89" s="135"/>
+      <c r="C89" s="135"/>
+      <c r="D89" s="135"/>
+      <c r="E89" s="135"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B88" s="46"/>
-      <c r="C88" s="24"/>
-    </row>
-    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="36" t="s">
+      <c r="B91" s="38"/>
+      <c r="C91" s="17"/>
+    </row>
+    <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B89" s="127">
-        <v>-149600.7575000003</v>
-      </c>
-      <c r="C89" s="26"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
+      <c r="B92" s="111">
+        <v>-1000157.7574999998</v>
+      </c>
+      <c r="C92" s="19"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B90" s="47">
+      <c r="B93" s="39">
         <f>PRORRATEO!H25</f>
-        <v>2639132.91</v>
-      </c>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="25" t="s">
+        <v>2893536.18</v>
+      </c>
+      <c r="C93" s="17"/>
+    </row>
+    <row r="94" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B91" s="55"/>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="133" t="s">
+      <c r="B94" s="47"/>
+      <c r="C94" s="17"/>
+    </row>
+    <row r="95" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="185" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="47">
+        <v>-8829</v>
+      </c>
+      <c r="C95" s="17"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B92" s="55"/>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="25" t="s">
+      <c r="B96" s="91">
+        <f>B115</f>
+        <v>262000</v>
+      </c>
+      <c r="C96" s="17"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B93" s="107">
-        <f>B112</f>
+      <c r="B97" s="47">
+        <f>-B82</f>
+        <v>-2670980.5599999996</v>
+      </c>
+      <c r="C97" s="17"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" s="47">
+        <f>-(B83)</f>
+        <v>-181000</v>
+      </c>
+      <c r="C98" s="17"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="110">
+        <f>SUM(B92:B98)</f>
+        <v>-705431.13749999925</v>
+      </c>
+      <c r="C99" s="20"/>
+    </row>
+    <row r="100" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="40"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="43"/>
+    </row>
+    <row r="101" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="41"/>
+      <c r="C101" s="20"/>
+    </row>
+    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="40"/>
+      <c r="C102" s="35"/>
+    </row>
+    <row r="103" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B103" s="33"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="46"/>
+    </row>
+    <row r="104" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B104" s="34">
         <v>0</v>
       </c>
-      <c r="C93" s="24"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="45" t="s">
+      <c r="C104" s="35"/>
+    </row>
+    <row r="105" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="33">
+        <v>0</v>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="43"/>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B106" s="33">
+        <v>0</v>
+      </c>
+      <c r="C106" s="20"/>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B94" s="55">
-        <f>-B79</f>
-        <v>-2961341.7800000003</v>
-      </c>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B95" s="55">
-        <f>-(B80)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C95" s="24"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="35" t="s">
+      <c r="B107" s="33">
+        <v>0</v>
+      </c>
+      <c r="C107" s="22"/>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B108" s="48">
+        <f>SUM(B104:B107)</f>
+        <v>0</v>
+      </c>
+      <c r="C108" s="17"/>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="143" t="s">
+        <v>59</v>
+      </c>
+      <c r="B111" s="135"/>
+      <c r="C111" s="135"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="135"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="135"/>
+    </row>
+    <row r="113" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="B113" s="33">
+        <v>262000</v>
+      </c>
+      <c r="C113" s="33">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="55"/>
+      <c r="B114" s="33"/>
+      <c r="C114" s="40"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B96" s="126">
-        <f>SUM(B89:B95)</f>
-        <v>-652809.62750000041</v>
-      </c>
-      <c r="C96" s="27"/>
-    </row>
-    <row r="97" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="48"/>
-      <c r="C97" s="27"/>
-      <c r="D97" s="51"/>
-    </row>
-    <row r="98" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="49"/>
-      <c r="C98" s="27"/>
-    </row>
-    <row r="99" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="48"/>
-      <c r="C99" s="43"/>
-    </row>
-    <row r="100" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B100" s="41"/>
-      <c r="C100" s="43"/>
-      <c r="D100" s="54"/>
-    </row>
-    <row r="101" spans="1:4" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B101" s="42">
-        <v>0</v>
-      </c>
-      <c r="C101" s="43"/>
-    </row>
-    <row r="102" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B102" s="41">
-        <v>0</v>
-      </c>
-      <c r="C102" s="27"/>
-      <c r="D102" s="51"/>
-    </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B103" s="41">
-        <v>0</v>
-      </c>
-      <c r="C103" s="27"/>
-    </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B104" s="41">
-        <v>0</v>
-      </c>
-      <c r="C104" s="29"/>
-    </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B105" s="56">
-        <f>SUM(B101:B104)</f>
-        <v>0</v>
-      </c>
-      <c r="C105" s="24"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="159" t="s">
-        <v>60</v>
-      </c>
-      <c r="B108" s="158"/>
-      <c r="C108" s="158"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="158"/>
-      <c r="B109" s="158"/>
-      <c r="C109" s="158"/>
-    </row>
-    <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="63"/>
-      <c r="B110" s="41"/>
-      <c r="C110" s="41">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="63"/>
-      <c r="B111" s="41"/>
-      <c r="C111" s="48"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B112" s="121">
-        <f>SUM(B110:B111)</f>
-        <v>0</v>
-      </c>
-      <c r="C112" s="53"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M113" s="8"/>
-    </row>
-    <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="165"/>
-      <c r="B114" s="158"/>
-      <c r="C114" s="158"/>
-      <c r="D114" s="158"/>
-      <c r="E114" s="158"/>
-    </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="158"/>
-      <c r="B115" s="158"/>
-      <c r="C115" s="158"/>
-      <c r="D115" s="158"/>
-      <c r="E115" s="158"/>
-    </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="158"/>
-      <c r="B116" s="158"/>
-      <c r="C116" s="158"/>
-      <c r="D116" s="158"/>
-      <c r="E116" s="158"/>
-    </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="158"/>
-      <c r="B117" s="158"/>
-      <c r="C117" s="158"/>
-      <c r="D117" s="158"/>
-      <c r="E117" s="158"/>
+      <c r="B115" s="105">
+        <f>SUM(B113:B114)</f>
+        <v>262000</v>
+      </c>
+      <c r="C115" s="45"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M116" s="8"/>
+    </row>
+    <row r="117" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="147"/>
+      <c r="B117" s="135"/>
+      <c r="C117" s="135"/>
+      <c r="D117" s="135"/>
+      <c r="E117" s="135"/>
+    </row>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="135"/>
+      <c r="B118" s="135"/>
+      <c r="C118" s="135"/>
+      <c r="D118" s="135"/>
+      <c r="E118" s="135"/>
+    </row>
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="135"/>
+      <c r="B119" s="135"/>
+      <c r="C119" s="135"/>
+      <c r="D119" s="135"/>
+      <c r="E119" s="135"/>
+    </row>
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="135"/>
+      <c r="B120" s="135"/>
+      <c r="C120" s="135"/>
+      <c r="D120" s="135"/>
+      <c r="E120" s="135"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A87:E89"/>
+    <mergeCell ref="A111:C112"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A72:B73"/>
+    <mergeCell ref="A117:E120"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A84:E86"/>
-    <mergeCell ref="A108:C109"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A69:B70"/>
-    <mergeCell ref="A114:E117"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2818,21 +2962,21 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="184" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2851,23 +2995,23 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="178">
+      <c r="O2" s="160">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="22"/>
+      <c r="P2" s="135"/>
+      <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -2877,147 +3021,147 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="182">
+      <c r="O3" s="164">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="183"/>
+      <c r="P3" s="165"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="158" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="179" t="s">
+      <c r="C4" s="151" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="174" t="s">
+      <c r="D4" s="151" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="174" t="s">
+      <c r="E4" s="153" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="175" t="s">
+      <c r="F4" s="151" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="174" t="s">
+      <c r="G4" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="174" t="s">
+      <c r="H4" s="151" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="174" t="s">
+      <c r="I4" s="153" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="175" t="s">
+      <c r="J4" s="156" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="185" t="s">
+      <c r="K4" s="159" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="177" t="s">
+      <c r="L4" s="157" t="s">
         <v>76</v>
       </c>
-      <c r="L4" s="186" t="s">
+      <c r="M4" s="159" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="177" t="s">
+      <c r="N4" s="159" t="s">
         <v>78</v>
       </c>
-      <c r="N4" s="177" t="s">
+      <c r="O4" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="O4" s="69" t="s">
+      <c r="P4" s="163" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="181" t="s">
-        <v>81</v>
-      </c>
-      <c r="S4" s="51"/>
+      <c r="S4" s="43"/>
       <c r="T4">
         <v>3000000</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="173"/>
-      <c r="B5" s="180"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
-      <c r="H5" s="173"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
-      <c r="O5" s="67" t="str">
+      <c r="A5" s="152"/>
+      <c r="B5" s="162"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="173"/>
+      <c r="P5" s="152"/>
     </row>
     <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="62">
+        <v>1</v>
+      </c>
+      <c r="C6" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="70">
-        <v>1</v>
-      </c>
-      <c r="C6" s="70" t="s">
+      <c r="D6" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="E6" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="80">
+      <c r="F6" s="68">
         <v>3</v>
       </c>
-      <c r="G6" s="147">
-        <v>79697.100000000006</v>
-      </c>
-      <c r="H6" s="148">
+      <c r="G6" s="168">
+        <v>95430.1</v>
+      </c>
+      <c r="H6" s="130">
         <f>G6</f>
-        <v>79697.100000000006</v>
-      </c>
-      <c r="I6" s="83"/>
-      <c r="J6" s="134">
+        <v>95430.1</v>
+      </c>
+      <c r="I6" s="70"/>
+      <c r="J6" s="117">
         <f t="shared" ref="J6:J24" si="0">G6-H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="84">
+      <c r="K6" s="71">
         <f t="shared" ref="K6:K24" si="1">IF(J6&gt;0,J6*5%,0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="85">
+      <c r="L6" s="72">
         <f t="shared" ref="L6:L24" si="2">O$3*F6%</f>
         <v>5430</v>
       </c>
-      <c r="M6" s="85">
+      <c r="M6" s="72">
         <f t="shared" ref="M6:M24" si="3">O$2*F6%</f>
         <v>90000</v>
       </c>
-      <c r="N6" s="130">
+      <c r="N6" s="114">
         <f t="shared" ref="N6:N24" si="4">SUM(J6:M6)</f>
         <v>95430</v>
       </c>
-      <c r="O6" s="135" t="str">
+      <c r="O6" s="118" t="str">
         <f t="shared" ref="O6:O24" si="5">CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
         <v>$95430,1</v>
       </c>
-      <c r="P6" s="136" t="str">
+      <c r="P6" s="119" t="str">
         <f t="shared" ref="P6:P24" si="6">CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
         <v>$98293,1</v>
       </c>
-      <c r="Q6" s="51" t="str">
+      <c r="Q6" s="43" t="str">
         <f t="shared" ref="Q6:Q24" si="7">CONCATENATE(B6)</f>
         <v>1</v>
       </c>
@@ -3027,1226 +3171,1217 @@
     </row>
     <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="62">
+        <v>2</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="70">
-        <v>2</v>
-      </c>
-      <c r="C7" s="70" t="s">
+      <c r="D7" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="E7" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="70" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="80">
+      <c r="F7" s="68">
         <v>3.8</v>
       </c>
-      <c r="G7" s="147">
-        <v>100950.2</v>
-      </c>
-      <c r="H7" s="148">
-        <v>103979.02</v>
-      </c>
-      <c r="I7" s="83"/>
-      <c r="J7" s="134">
+      <c r="G7" s="168">
+        <v>117849.2</v>
+      </c>
+      <c r="H7" s="130">
+        <f>G7</f>
+        <v>117849.2</v>
+      </c>
+      <c r="I7" s="70"/>
+      <c r="J7" s="117">
         <f t="shared" si="0"/>
-        <v>-3028.820000000007</v>
-      </c>
-      <c r="K7" s="84">
+        <v>0</v>
+      </c>
+      <c r="K7" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L7" s="85">
+      <c r="L7" s="72">
         <f t="shared" si="2"/>
         <v>6878</v>
       </c>
-      <c r="M7" s="85">
+      <c r="M7" s="72">
         <f t="shared" si="3"/>
         <v>114000</v>
       </c>
-      <c r="N7" s="130">
+      <c r="N7" s="114">
         <f t="shared" si="4"/>
-        <v>117849.18</v>
-      </c>
-      <c r="O7" s="132" t="str">
+        <v>120878</v>
+      </c>
+      <c r="O7" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$117849,2</v>
-      </c>
-      <c r="P7" s="136" t="str">
+        <v>$120878,2</v>
+      </c>
+      <c r="P7" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$121385,2</v>
-      </c>
-      <c r="Q7" s="51" t="str">
+        <v>$124504,2</v>
+      </c>
+      <c r="Q7" s="43" t="str">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="R7" s="51"/>
+      <c r="R7" s="43"/>
     </row>
     <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="70">
+        <v>85</v>
+      </c>
+      <c r="B8" s="62">
         <v>3</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="E8" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="80">
+      <c r="F8" s="68">
         <v>3</v>
       </c>
-      <c r="G8" s="147">
-        <v>82088.3</v>
-      </c>
-      <c r="H8" s="148">
+      <c r="G8" s="168">
+        <v>98293.3</v>
+      </c>
+      <c r="H8" s="130">
         <f>G8</f>
-        <v>82088.3</v>
-      </c>
-      <c r="I8" s="83"/>
-      <c r="J8" s="134">
+        <v>98293.3</v>
+      </c>
+      <c r="I8" s="70"/>
+      <c r="J8" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="72">
         <f t="shared" si="2"/>
         <v>5430</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="72">
         <f t="shared" si="3"/>
         <v>90000</v>
       </c>
-      <c r="N8" s="130">
+      <c r="N8" s="114">
         <f t="shared" si="4"/>
         <v>95430</v>
       </c>
-      <c r="O8" s="132" t="str">
+      <c r="O8" s="116" t="str">
         <f t="shared" si="5"/>
         <v>$95430,3</v>
       </c>
-      <c r="P8" s="136" t="str">
+      <c r="P8" s="119" t="str">
         <f t="shared" si="6"/>
         <v>$98293,3</v>
       </c>
-      <c r="Q8" s="51" t="str">
+      <c r="Q8" s="43" t="str">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="62">
+        <v>4</v>
+      </c>
+      <c r="C9" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="70">
-        <v>4</v>
-      </c>
-      <c r="C9" s="70" t="s">
+      <c r="D9" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="E9" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="80">
+      <c r="F9" s="68">
         <v>3.1</v>
       </c>
-      <c r="G9" s="147">
-        <v>235782.39999999999</v>
-      </c>
-      <c r="H9" s="148">
-        <v>80000.039999999994</v>
-      </c>
-      <c r="I9" s="83"/>
-      <c r="J9" s="134">
+      <c r="G9" s="168">
+        <v>270048.03999999998</v>
+      </c>
+      <c r="H9" s="130">
+        <f>G9</f>
+        <v>270048.03999999998</v>
+      </c>
+      <c r="I9" s="70"/>
+      <c r="J9" s="117">
         <f t="shared" si="0"/>
-        <v>155782.35999999999</v>
-      </c>
-      <c r="K9" s="84">
+        <v>0</v>
+      </c>
+      <c r="K9" s="71">
         <f t="shared" si="1"/>
-        <v>7789.1179999999995</v>
-      </c>
-      <c r="L9" s="85">
+        <v>0</v>
+      </c>
+      <c r="L9" s="72">
         <f t="shared" si="2"/>
         <v>5611</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="72">
         <f t="shared" si="3"/>
         <v>93000</v>
       </c>
-      <c r="N9" s="130">
+      <c r="N9" s="114">
         <f t="shared" si="4"/>
-        <v>262182.478</v>
-      </c>
-      <c r="O9" s="132" t="str">
+        <v>98611</v>
+      </c>
+      <c r="O9" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$262182,4</v>
-      </c>
-      <c r="P9" s="136" t="str">
+        <v>$98611,4</v>
+      </c>
+      <c r="P9" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$270048,4</v>
-      </c>
-      <c r="Q9" s="51" t="str">
+        <v>$101569,4</v>
+      </c>
+      <c r="Q9" s="43" t="str">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="S9" s="51"/>
+      <c r="S9" s="43"/>
     </row>
     <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="70">
+        <v>92</v>
+      </c>
+      <c r="B10" s="62">
         <v>5</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="E10" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="F10" s="68">
+        <v>3.1</v>
+      </c>
+      <c r="G10" s="168">
+        <v>98611.5</v>
+      </c>
+      <c r="H10" s="130"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="117">
+        <f t="shared" si="0"/>
+        <v>98611.5</v>
+      </c>
+      <c r="K10" s="71">
+        <f t="shared" si="1"/>
+        <v>4930.5750000000007</v>
+      </c>
+      <c r="L10" s="72">
+        <f t="shared" si="2"/>
+        <v>5611</v>
+      </c>
+      <c r="M10" s="72">
+        <f t="shared" si="3"/>
+        <v>93000</v>
+      </c>
+      <c r="N10" s="114">
+        <f t="shared" si="4"/>
+        <v>202153.07500000001</v>
+      </c>
+      <c r="O10" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$202153,5</v>
+      </c>
+      <c r="P10" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$208218,5</v>
+      </c>
+      <c r="Q10" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S10" s="43"/>
+    </row>
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="80">
-        <v>3.1</v>
-      </c>
-      <c r="G10" s="147">
-        <v>224424.5</v>
-      </c>
-      <c r="H10" s="148">
-        <f>G10</f>
-        <v>224424.5</v>
-      </c>
-      <c r="I10" s="83"/>
-      <c r="J10" s="134">
+      <c r="B11" s="62">
+        <v>6</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="68">
+        <v>3.2</v>
+      </c>
+      <c r="G11" s="168">
+        <v>101792.6</v>
+      </c>
+      <c r="H11" s="130">
+        <f>G11</f>
+        <v>101792.6</v>
+      </c>
+      <c r="I11" s="70"/>
+      <c r="J11" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="84">
+      <c r="K11" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L10" s="85">
+      <c r="L11" s="72">
         <f t="shared" si="2"/>
-        <v>5611</v>
-      </c>
-      <c r="M10" s="85">
+        <v>5792</v>
+      </c>
+      <c r="M11" s="72">
         <f t="shared" si="3"/>
-        <v>93000</v>
-      </c>
-      <c r="N10" s="130">
+        <v>96000</v>
+      </c>
+      <c r="N11" s="114">
         <f t="shared" si="4"/>
-        <v>98611</v>
-      </c>
-      <c r="O10" s="132" t="str">
+        <v>101792</v>
+      </c>
+      <c r="O11" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$98611,5</v>
-      </c>
-      <c r="P10" s="136" t="str">
+        <v>$101792,6</v>
+      </c>
+      <c r="P11" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$101569,5</v>
-      </c>
-      <c r="Q10" s="51" t="str">
+        <v>$104846,6</v>
+      </c>
+      <c r="Q11" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="S10" s="51"/>
-    </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="70">
         <v>6</v>
       </c>
-      <c r="C11" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="70" t="s">
+    </row>
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="62">
+        <v>7</v>
+      </c>
+      <c r="C12" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="80">
-        <v>3.2</v>
-      </c>
-      <c r="G11" s="147">
-        <v>81011.600000000006</v>
-      </c>
-      <c r="H11" s="148">
-        <f>G11</f>
-        <v>81011.600000000006</v>
-      </c>
-      <c r="I11" s="83"/>
-      <c r="J11" s="134">
+      <c r="D12" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="68">
+        <v>3.3</v>
+      </c>
+      <c r="G12" s="168">
+        <v>102343.7</v>
+      </c>
+      <c r="H12" s="130">
+        <f>G12</f>
+        <v>102343.7</v>
+      </c>
+      <c r="I12" s="70"/>
+      <c r="J12" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="84">
+      <c r="K12" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L11" s="85">
+      <c r="L12" s="72">
         <f t="shared" si="2"/>
-        <v>5792</v>
-      </c>
-      <c r="M11" s="85">
+        <v>5973</v>
+      </c>
+      <c r="M12" s="72">
         <f t="shared" si="3"/>
-        <v>96000</v>
-      </c>
-      <c r="N11" s="130">
+        <v>99000</v>
+      </c>
+      <c r="N12" s="114">
         <f t="shared" si="4"/>
-        <v>101792</v>
-      </c>
-      <c r="O11" s="132" t="str">
+        <v>104973</v>
+      </c>
+      <c r="O12" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$101792,6</v>
-      </c>
-      <c r="P11" s="136" t="str">
+        <v>$104973,7</v>
+      </c>
+      <c r="P12" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$104846,6</v>
-      </c>
-      <c r="Q11" s="51" t="str">
+        <v>$108122,7</v>
+      </c>
+      <c r="Q12" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="70">
         <v>7</v>
       </c>
-      <c r="C12" s="70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="70" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="70" t="s">
+    </row>
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="80">
-        <v>3.3</v>
-      </c>
-      <c r="G12" s="147">
-        <v>87667.7</v>
-      </c>
-      <c r="H12" s="148">
-        <v>90297.7</v>
-      </c>
-      <c r="I12" s="83"/>
-      <c r="J12" s="134">
+      <c r="B13" s="62">
+        <v>23</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="68">
+        <v>6.3</v>
+      </c>
+      <c r="G13" s="168">
+        <v>200403.23</v>
+      </c>
+      <c r="H13" s="69">
+        <v>189000</v>
+      </c>
+      <c r="I13" s="70"/>
+      <c r="J13" s="117">
         <f t="shared" si="0"/>
-        <v>-2630</v>
-      </c>
-      <c r="K12" s="84">
+        <v>11403.23000000001</v>
+      </c>
+      <c r="K13" s="71">
+        <f t="shared" si="1"/>
+        <v>570.1615000000005</v>
+      </c>
+      <c r="L13" s="72">
+        <f t="shared" si="2"/>
+        <v>11403</v>
+      </c>
+      <c r="M13" s="72">
+        <f t="shared" si="3"/>
+        <v>189000</v>
+      </c>
+      <c r="N13" s="114">
+        <f t="shared" si="4"/>
+        <v>212376.39150000003</v>
+      </c>
+      <c r="O13" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$212376,23</v>
+      </c>
+      <c r="P13" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$218748,23</v>
+      </c>
+      <c r="Q13" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="S13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="62">
+        <v>22</v>
+      </c>
+      <c r="C14" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="68">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G14" s="168">
+        <v>162231.22</v>
+      </c>
+      <c r="H14" s="69">
+        <f>G14</f>
+        <v>162231.22</v>
+      </c>
+      <c r="I14" s="70"/>
+      <c r="J14" s="117">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L12" s="85">
+      <c r="L14" s="72">
         <f t="shared" si="2"/>
-        <v>5973</v>
-      </c>
-      <c r="M12" s="85">
+        <v>9231</v>
+      </c>
+      <c r="M14" s="72">
         <f t="shared" si="3"/>
-        <v>99000</v>
-      </c>
-      <c r="N12" s="130">
+        <v>153000</v>
+      </c>
+      <c r="N14" s="114">
         <f t="shared" si="4"/>
-        <v>102343</v>
-      </c>
-      <c r="O12" s="132" t="str">
+        <v>162231</v>
+      </c>
+      <c r="O14" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$102343,7</v>
-      </c>
-      <c r="P12" s="136" t="str">
+        <v>$162231,22</v>
+      </c>
+      <c r="P14" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$105413,7</v>
-      </c>
-      <c r="Q12" s="51" t="str">
+        <v>$167098,22</v>
+      </c>
+      <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="70">
-        <v>23</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="70" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="80">
-        <v>6.3</v>
-      </c>
-      <c r="G13" s="81">
-        <v>180595.23</v>
-      </c>
-      <c r="H13" s="82">
-        <f>177613+2982.23</f>
-        <v>180595.23</v>
-      </c>
-      <c r="I13" s="83"/>
-      <c r="J13" s="134">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="62">
+        <v>21</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="63"/>
+      <c r="F15" s="68">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G15" s="168">
+        <v>264918.21000000002</v>
+      </c>
+      <c r="H15" s="69">
+        <f>G15</f>
+        <v>264918.21000000002</v>
+      </c>
+      <c r="I15" s="70"/>
+      <c r="J15" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="84">
+      <c r="K15" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="85">
+      <c r="L15" s="72">
         <f t="shared" si="2"/>
-        <v>11403</v>
-      </c>
-      <c r="M13" s="85">
+        <v>14841.999999999998</v>
+      </c>
+      <c r="M15" s="72">
         <f t="shared" si="3"/>
-        <v>189000</v>
-      </c>
-      <c r="N13" s="130">
+        <v>245999.99999999997</v>
+      </c>
+      <c r="N15" s="114">
         <f t="shared" si="4"/>
-        <v>200403</v>
-      </c>
-      <c r="O13" s="132" t="str">
+        <v>260841.99999999997</v>
+      </c>
+      <c r="O15" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$200403,23</v>
-      </c>
-      <c r="P13" s="136" t="str">
+        <v>$260842,21</v>
+      </c>
+      <c r="P15" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$206415,23</v>
-      </c>
-      <c r="Q13" s="51" t="str">
+        <v>$268667,21</v>
+      </c>
+      <c r="Q15" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>23</v>
-      </c>
-      <c r="S13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="70">
-        <v>22</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="70" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="80">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G14" s="81">
-        <v>135696.22</v>
-      </c>
-      <c r="H14" s="82">
-        <v>135696.22</v>
-      </c>
-      <c r="I14" s="83"/>
-      <c r="J14" s="134">
+      <c r="B16" s="62">
+        <v>14</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="68">
+        <v>6.1</v>
+      </c>
+      <c r="G16" s="168">
+        <v>194041.14</v>
+      </c>
+      <c r="H16" s="69">
+        <f>G16</f>
+        <v>194041.14</v>
+      </c>
+      <c r="I16" s="70"/>
+      <c r="J16" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="84">
+      <c r="K16" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L14" s="85">
+      <c r="L16" s="72">
         <f t="shared" si="2"/>
-        <v>9231</v>
-      </c>
-      <c r="M14" s="85">
+        <v>11041</v>
+      </c>
+      <c r="M16" s="72">
         <f t="shared" si="3"/>
-        <v>153000</v>
-      </c>
-      <c r="N14" s="130">
+        <v>183000</v>
+      </c>
+      <c r="N16" s="114">
         <f t="shared" si="4"/>
-        <v>162231</v>
-      </c>
-      <c r="O14" s="132" t="str">
+        <v>194041</v>
+      </c>
+      <c r="O16" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$162231,22</v>
-      </c>
-      <c r="P14" s="136" t="str">
+        <v>$194041,14</v>
+      </c>
+      <c r="P16" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$167098,22</v>
-      </c>
-      <c r="Q14" s="51" t="str">
+        <v>$199862,14</v>
+      </c>
+      <c r="Q16" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="70">
-        <v>21</v>
-      </c>
-      <c r="C15" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="71"/>
-      <c r="F15" s="80">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="62">
+        <v>13</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="62" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="63"/>
+      <c r="F17" s="68">
+        <v>5</v>
+      </c>
+      <c r="G17" s="168">
+        <v>155065.13</v>
+      </c>
+      <c r="H17" s="69">
+        <v>159717.13</v>
+      </c>
+      <c r="I17" s="70"/>
+      <c r="J17" s="117">
+        <f t="shared" si="0"/>
+        <v>-4652</v>
+      </c>
+      <c r="K17" s="71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="72">
+        <f t="shared" si="2"/>
+        <v>9050</v>
+      </c>
+      <c r="M17" s="72">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="N17" s="114">
+        <f t="shared" si="4"/>
+        <v>154398</v>
+      </c>
+      <c r="O17" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$154398,13</v>
+      </c>
+      <c r="P17" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$159030,13</v>
+      </c>
+      <c r="Q17" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="62">
+        <v>12</v>
+      </c>
+      <c r="C18" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G15" s="81">
-        <v>217840.21</v>
-      </c>
-      <c r="H15" s="82">
-        <v>213958.21</v>
-      </c>
-      <c r="I15" s="83"/>
-      <c r="J15" s="134">
+      <c r="G18" s="168">
+        <v>14360927.119999999</v>
+      </c>
+      <c r="H18" s="69">
+        <v>260842</v>
+      </c>
+      <c r="I18" s="70"/>
+      <c r="J18" s="117">
         <f t="shared" si="0"/>
-        <v>3882</v>
-      </c>
-      <c r="K15" s="84">
+        <v>14100085.119999999</v>
+      </c>
+      <c r="K18" s="71">
         <f t="shared" si="1"/>
-        <v>194.10000000000002</v>
-      </c>
-      <c r="L15" s="85">
+        <v>705004.25600000005</v>
+      </c>
+      <c r="L18" s="72">
         <f t="shared" si="2"/>
         <v>14841.999999999998</v>
       </c>
-      <c r="M15" s="85">
+      <c r="M18" s="72">
         <f t="shared" si="3"/>
         <v>245999.99999999997</v>
       </c>
-      <c r="N15" s="130">
+      <c r="N18" s="114">
         <f t="shared" si="4"/>
-        <v>264918.09999999998</v>
-      </c>
-      <c r="O15" s="132" t="str">
+        <v>15065931.375999998</v>
+      </c>
+      <c r="O18" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$264918,21</v>
-      </c>
-      <c r="P15" s="136" t="str">
+        <v>$15065931,12</v>
+      </c>
+      <c r="P18" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$272866,21</v>
-      </c>
-      <c r="Q15" s="51" t="str">
+        <v>$15517909,12</v>
+      </c>
+      <c r="Q18" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="70">
-        <v>14</v>
-      </c>
-      <c r="C16" s="70" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="80">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="62">
+        <v>17</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="63"/>
+      <c r="F19" s="68">
         <v>6.1</v>
       </c>
-      <c r="G16" s="81">
-        <v>162052.14000000001</v>
-      </c>
-      <c r="H16" s="82">
-        <f>G16</f>
-        <v>162052.14000000001</v>
-      </c>
-      <c r="I16" s="83"/>
-      <c r="J16" s="134">
+      <c r="G19" s="168">
+        <v>10194042.17</v>
+      </c>
+      <c r="H19" s="69"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="117">
+        <f t="shared" si="0"/>
+        <v>10194042.17</v>
+      </c>
+      <c r="K19" s="71">
+        <f t="shared" si="1"/>
+        <v>509702.10850000003</v>
+      </c>
+      <c r="L19" s="72">
+        <f t="shared" si="2"/>
+        <v>11041</v>
+      </c>
+      <c r="M19" s="72">
+        <f t="shared" si="3"/>
+        <v>183000</v>
+      </c>
+      <c r="N19" s="114">
+        <f t="shared" si="4"/>
+        <v>10897785.2785</v>
+      </c>
+      <c r="O19" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$10897785,17</v>
+      </c>
+      <c r="P19" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$11224719,17</v>
+      </c>
+      <c r="Q19" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="62">
+        <v>16</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="68">
+        <v>5</v>
+      </c>
+      <c r="G20" s="169">
+        <v>168321.16</v>
+      </c>
+      <c r="H20" s="69">
+        <f>G20</f>
+        <v>168321.16</v>
+      </c>
+      <c r="I20" s="70"/>
+      <c r="J20" s="117">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="84">
+      <c r="K20" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L16" s="85">
+      <c r="L20" s="72">
+        <f t="shared" si="2"/>
+        <v>9050</v>
+      </c>
+      <c r="M20" s="72">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="N20" s="114">
+        <f t="shared" si="4"/>
+        <v>159050</v>
+      </c>
+      <c r="O20" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$159050,16</v>
+      </c>
+      <c r="P20" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$163822,16</v>
+      </c>
+      <c r="Q20" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="S20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="62">
+        <v>15</v>
+      </c>
+      <c r="C21" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="62"/>
+      <c r="F21" s="68">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G21" s="168">
+        <v>264918.15000000002</v>
+      </c>
+      <c r="H21" s="69">
+        <v>246000</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="117">
+        <f t="shared" si="0"/>
+        <v>18918.150000000023</v>
+      </c>
+      <c r="K21" s="71">
+        <f t="shared" si="1"/>
+        <v>945.90750000000116</v>
+      </c>
+      <c r="L21" s="72">
+        <f t="shared" si="2"/>
+        <v>14841.999999999998</v>
+      </c>
+      <c r="M21" s="72">
+        <f t="shared" si="3"/>
+        <v>245999.99999999997</v>
+      </c>
+      <c r="N21" s="114">
+        <f t="shared" si="4"/>
+        <v>280706.0575</v>
+      </c>
+      <c r="O21" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$280706,15</v>
+      </c>
+      <c r="P21" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$289127,15</v>
+      </c>
+      <c r="Q21" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="S21" s="42"/>
+    </row>
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="62">
+        <v>20</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="63"/>
+      <c r="F22" s="68">
+        <v>6.1</v>
+      </c>
+      <c r="G22" s="169">
+        <v>194041.2</v>
+      </c>
+      <c r="H22" s="69">
+        <f>G22</f>
+        <v>194041.2</v>
+      </c>
+      <c r="I22" s="70"/>
+      <c r="J22" s="71">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="72">
         <f t="shared" si="2"/>
         <v>11041</v>
       </c>
-      <c r="M16" s="85">
+      <c r="M22" s="72">
         <f t="shared" si="3"/>
         <v>183000</v>
       </c>
-      <c r="N16" s="130">
+      <c r="N22" s="114">
         <f t="shared" si="4"/>
         <v>194041</v>
       </c>
-      <c r="O16" s="132" t="str">
+      <c r="O22" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$194041,14</v>
-      </c>
-      <c r="P16" s="136" t="str">
+        <v>$194041,20</v>
+      </c>
+      <c r="P22" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$199862,14</v>
-      </c>
-      <c r="Q16" s="51" t="str">
+        <v>$199862,20</v>
+      </c>
+      <c r="Q22" s="43" t="str">
         <f t="shared" si="7"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="70">
-        <v>13</v>
-      </c>
-      <c r="C17" s="70" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="80">
+        <v>20</v>
+      </c>
+      <c r="T22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="62">
+        <v>19</v>
+      </c>
+      <c r="C23" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="62" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="68">
         <v>5</v>
       </c>
-      <c r="G17" s="81">
-        <v>132829.13</v>
-      </c>
-      <c r="H17" s="82">
-        <v>136814.13</v>
-      </c>
-      <c r="I17" s="83"/>
-      <c r="J17" s="134">
+      <c r="G23" s="168">
+        <v>159050.19</v>
+      </c>
+      <c r="H23" s="69"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="71">
         <f t="shared" si="0"/>
-        <v>-3985</v>
-      </c>
-      <c r="K17" s="84">
+        <v>159050.19</v>
+      </c>
+      <c r="K23" s="71">
+        <f t="shared" si="1"/>
+        <v>7952.5095000000001</v>
+      </c>
+      <c r="L23" s="72">
+        <f t="shared" si="2"/>
+        <v>9050</v>
+      </c>
+      <c r="M23" s="72">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="N23" s="114">
+        <f t="shared" si="4"/>
+        <v>326052.69949999999</v>
+      </c>
+      <c r="O23" s="116" t="str">
+        <f t="shared" si="5"/>
+        <v>$326053,19</v>
+      </c>
+      <c r="P23" s="119" t="str">
+        <f t="shared" si="6"/>
+        <v>$335834,19</v>
+      </c>
+      <c r="Q23" s="43" t="str">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="62">
+        <v>18</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" s="63"/>
+      <c r="F24" s="68">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G24" s="168">
+        <v>260842.18</v>
+      </c>
+      <c r="H24" s="69">
+        <f>268667.18</f>
+        <v>268667.18</v>
+      </c>
+      <c r="I24" s="70"/>
+      <c r="J24" s="71">
+        <f t="shared" si="0"/>
+        <v>-7825</v>
+      </c>
+      <c r="K24" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L17" s="85">
-        <f t="shared" si="2"/>
-        <v>9050</v>
-      </c>
-      <c r="M17" s="85">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-      <c r="N17" s="130">
-        <f t="shared" si="4"/>
-        <v>155065</v>
-      </c>
-      <c r="O17" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$155065,13</v>
-      </c>
-      <c r="P17" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$159717,13</v>
-      </c>
-      <c r="Q17" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="70">
-        <v>12</v>
-      </c>
-      <c r="C18" s="70" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="F18" s="80">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="G18" s="81">
-        <v>13646491.119999999</v>
-      </c>
-      <c r="H18" s="82">
-        <v>217839</v>
-      </c>
-      <c r="I18" s="83"/>
-      <c r="J18" s="134">
-        <f t="shared" si="0"/>
-        <v>13428652.119999999</v>
-      </c>
-      <c r="K18" s="84">
-        <f t="shared" si="1"/>
-        <v>671432.60600000003</v>
-      </c>
-      <c r="L18" s="85">
+      <c r="L24" s="72">
         <f t="shared" si="2"/>
         <v>14841.999999999998</v>
       </c>
-      <c r="M18" s="85">
+      <c r="M24" s="72">
         <f t="shared" si="3"/>
         <v>245999.99999999997</v>
       </c>
-      <c r="N18" s="130">
+      <c r="N24" s="114">
         <f t="shared" si="4"/>
-        <v>14360926.726</v>
-      </c>
-      <c r="O18" s="132" t="str">
+        <v>253016.99999999997</v>
+      </c>
+      <c r="O24" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$14360927,12</v>
-      </c>
-      <c r="P18" s="136" t="str">
+        <v>$253017,18</v>
+      </c>
+      <c r="P24" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$14791755,12</v>
-      </c>
-      <c r="Q18" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="70">
-        <v>17</v>
-      </c>
-      <c r="C19" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="71"/>
-      <c r="F19" s="80">
-        <v>6.1</v>
-      </c>
-      <c r="G19" s="81">
-        <v>9523810.1699999999</v>
-      </c>
-      <c r="H19" s="82"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="134">
-        <f t="shared" si="0"/>
-        <v>9523810.1699999999</v>
-      </c>
-      <c r="K19" s="84">
-        <f t="shared" si="1"/>
-        <v>476190.5085</v>
-      </c>
-      <c r="L19" s="85">
-        <f t="shared" si="2"/>
-        <v>11041</v>
-      </c>
-      <c r="M19" s="85">
-        <f t="shared" si="3"/>
-        <v>183000</v>
-      </c>
-      <c r="N19" s="130">
-        <f t="shared" si="4"/>
-        <v>10194041.6785</v>
-      </c>
-      <c r="O19" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$10194042,17</v>
-      </c>
-      <c r="P19" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$10499863,17</v>
-      </c>
-      <c r="Q19" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="70">
-        <v>16</v>
-      </c>
-      <c r="C20" s="70" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="70" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" s="71" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="80">
-        <v>5</v>
-      </c>
-      <c r="G20" s="151">
-        <v>132829.16</v>
-      </c>
-      <c r="H20" s="151">
-        <f>118000+5000+1000</f>
-        <v>124000</v>
-      </c>
-      <c r="I20" s="83"/>
-      <c r="J20" s="134">
-        <f t="shared" si="0"/>
-        <v>8829.1600000000035</v>
-      </c>
-      <c r="K20" s="84">
-        <f t="shared" si="1"/>
-        <v>441.4580000000002</v>
-      </c>
-      <c r="L20" s="85">
-        <f t="shared" si="2"/>
-        <v>9050</v>
-      </c>
-      <c r="M20" s="85">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-      <c r="N20" s="130">
-        <f t="shared" si="4"/>
-        <v>168320.61800000002</v>
-      </c>
-      <c r="O20" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$168321,16</v>
-      </c>
-      <c r="P20" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$173370,16</v>
-      </c>
-      <c r="Q20" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>16</v>
-      </c>
-      <c r="S20" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B21" s="70">
-        <v>15</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" s="70"/>
-      <c r="F21" s="80">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="G21" s="81">
-        <v>217840.15</v>
-      </c>
-      <c r="H21" s="82">
-        <v>213958.15</v>
-      </c>
-      <c r="I21" s="83"/>
-      <c r="J21" s="134">
-        <f t="shared" si="0"/>
-        <v>3882</v>
-      </c>
-      <c r="K21" s="84">
-        <f t="shared" si="1"/>
-        <v>194.10000000000002</v>
-      </c>
-      <c r="L21" s="85">
-        <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
-      </c>
-      <c r="M21" s="85">
-        <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
-      </c>
-      <c r="N21" s="130">
-        <f t="shared" si="4"/>
-        <v>264918.09999999998</v>
-      </c>
-      <c r="O21" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$264918,15</v>
-      </c>
-      <c r="P21" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$272866,15</v>
-      </c>
-      <c r="Q21" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="S21" s="50"/>
-    </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" s="70">
-        <v>20</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="70" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="71"/>
-      <c r="F22" s="80">
-        <v>6.1</v>
-      </c>
-      <c r="G22" s="82">
-        <v>162052.20000000001</v>
-      </c>
-      <c r="H22" s="82">
-        <f>G22</f>
-        <v>162052.20000000001</v>
-      </c>
-      <c r="I22" s="83"/>
-      <c r="J22" s="84">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="85">
-        <f t="shared" si="2"/>
-        <v>11041</v>
-      </c>
-      <c r="M22" s="85">
-        <f t="shared" si="3"/>
-        <v>183000</v>
-      </c>
-      <c r="N22" s="130">
-        <f t="shared" si="4"/>
-        <v>194041</v>
-      </c>
-      <c r="O22" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$194041,20</v>
-      </c>
-      <c r="P22" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$199862,20</v>
-      </c>
-      <c r="Q22" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="T22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="70">
-        <v>19</v>
-      </c>
-      <c r="C23" s="70" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="70"/>
-      <c r="F23" s="80">
-        <v>5</v>
-      </c>
-      <c r="G23" s="81">
-        <v>132829.19</v>
-      </c>
-      <c r="H23" s="82">
-        <f>G23</f>
-        <v>132829.19</v>
-      </c>
-      <c r="I23" s="83"/>
-      <c r="J23" s="84">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="85">
-        <f t="shared" si="2"/>
-        <v>9050</v>
-      </c>
-      <c r="M23" s="85">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-      <c r="N23" s="130">
-        <f t="shared" si="4"/>
-        <v>159050</v>
-      </c>
-      <c r="O23" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$159050,19</v>
-      </c>
-      <c r="P23" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$163822,19</v>
-      </c>
-      <c r="Q23" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="70">
-        <v>18</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" s="71"/>
-      <c r="F24" s="80">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="G24" s="81">
-        <v>217840.18</v>
-      </c>
-      <c r="H24" s="82">
-        <f>G24</f>
-        <v>217840.18</v>
-      </c>
-      <c r="I24" s="83"/>
-      <c r="J24" s="84">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="85">
-        <f t="shared" si="2"/>
-        <v>14841.999999999998</v>
-      </c>
-      <c r="M24" s="85">
-        <f t="shared" si="3"/>
-        <v>245999.99999999997</v>
-      </c>
-      <c r="N24" s="130">
-        <f t="shared" si="4"/>
-        <v>260841.99999999997</v>
-      </c>
-      <c r="O24" s="132" t="str">
-        <f t="shared" si="5"/>
-        <v>$260842,18</v>
-      </c>
-      <c r="P24" s="136" t="str">
-        <f t="shared" si="6"/>
-        <v>$268667,18</v>
-      </c>
-      <c r="Q24" s="51" t="str">
+        <v>$260608,18</v>
+      </c>
+      <c r="Q24" s="43" t="str">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="86"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="89">
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76">
         <f t="shared" ref="F25:M25" si="8">SUM(F6:F24)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="G25" s="62">
+      <c r="G25" s="54">
         <f t="shared" si="8"/>
-        <v>25754326.899999999</v>
-      </c>
-      <c r="H25" s="68">
+        <v>27463169.539999995</v>
+      </c>
+      <c r="H25" s="60">
         <f t="shared" si="8"/>
-        <v>2639132.91</v>
-      </c>
-      <c r="I25" s="62">
+        <v>2893536.18</v>
+      </c>
+      <c r="I25" s="54">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J25" s="68">
+      <c r="J25" s="60">
         <f t="shared" si="8"/>
-        <v>23115193.989999998</v>
-      </c>
-      <c r="K25" s="68">
+        <v>24569633.359999999</v>
+      </c>
+      <c r="K25" s="60">
         <f t="shared" si="8"/>
-        <v>1156241.8905000002</v>
-      </c>
-      <c r="L25" s="68">
+        <v>1229105.5179999999</v>
+      </c>
+      <c r="L25" s="60">
         <f t="shared" si="8"/>
         <v>181000</v>
       </c>
-      <c r="M25" s="68">
+      <c r="M25" s="60">
         <f t="shared" si="8"/>
         <v>3000000</v>
       </c>
-      <c r="N25" s="131"/>
-      <c r="O25" s="90">
+      <c r="N25" s="115"/>
+      <c r="O25" s="77">
         <f>SUM(O6:O24)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="90">
+      <c r="P25" s="77">
         <f>SUM(P6:P24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="165" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158"/>
-      <c r="J28" s="158"/>
-      <c r="K28" s="158"/>
-      <c r="L28" s="158"/>
-      <c r="M28" s="158"/>
-      <c r="N28" s="158"/>
-      <c r="O28" s="158"/>
+      <c r="D28" s="147" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="135"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="135"/>
+      <c r="N28" s="135"/>
+      <c r="O28" s="135"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="158"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="158"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="158"/>
-      <c r="O29" s="158"/>
+      <c r="D29" s="135"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="135"/>
+      <c r="I29" s="135"/>
+      <c r="J29" s="135"/>
+      <c r="K29" s="135"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="135"/>
+      <c r="N29" s="135"/>
+      <c r="O29" s="135"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="158"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135"/>
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+      <c r="N30" s="135"/>
+      <c r="O30" s="135"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="158"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="158"/>
-      <c r="O31" s="158"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="135"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="135"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="135"/>
+      <c r="N31" s="135"/>
+      <c r="O31" s="135"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="158"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="158"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="158"/>
-      <c r="M32" s="158"/>
-      <c r="N32" s="158"/>
-      <c r="O32" s="158"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="135"/>
+      <c r="K32" s="135"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="135"/>
+      <c r="N32" s="135"/>
+      <c r="O32" s="135"/>
     </row>
     <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="158"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="158"/>
-      <c r="M33" s="158"/>
-      <c r="N33" s="158"/>
-      <c r="O33" s="158"/>
-      <c r="R33" s="152" t="s">
-        <v>154</v>
-      </c>
-      <c r="S33" s="152"/>
-      <c r="T33" s="152"/>
-      <c r="U33" s="152"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="135"/>
+      <c r="K33" s="135"/>
+      <c r="L33" s="135"/>
+      <c r="M33" s="135"/>
+      <c r="N33" s="135"/>
+      <c r="O33" s="135"/>
+      <c r="R33" s="104"/>
+      <c r="S33" s="104"/>
+      <c r="T33" s="104"/>
+      <c r="U33" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4259,6 +4394,13 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
+++ b/PUEYRREDON 1494/Julio/PUEYRREDON Julio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7100A170-7E8F-4AE5-A09C-997CB59F99F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526A91AB-E863-4823-9701-8AC5CB318D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="171">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -535,6 +535,9 @@
   </si>
   <si>
     <t>11/07 Transf no identificada - Valentina Cecilia Zarate</t>
+  </si>
+  <si>
+    <t>EL PAGO NO IDENTIFICADO DEL MES PASADO ES DE ELLA - RATON MARIELA</t>
   </si>
 </sst>
 </file>
@@ -749,7 +752,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -816,6 +819,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1217,7 +1226,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1396,99 +1405,17 @@
     </xf>
     <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1504,8 +1431,92 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1876,121 +1887,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="175"/>
-      <c r="B1" s="176"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="178"/>
+      <c r="A1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="144"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="179"/>
-      <c r="B2" s="171" t="s">
+      <c r="A2" s="145"/>
+      <c r="B2" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="180"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="146"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="179"/>
-      <c r="B3" s="171" t="s">
+      <c r="A3" s="145"/>
+      <c r="B3" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="180"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="146"/>
     </row>
     <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179"/>
-      <c r="B4" s="172" t="s">
+      <c r="A4" s="145"/>
+      <c r="B4" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="171"/>
-      <c r="D4" s="173" t="s">
+      <c r="C4" s="137"/>
+      <c r="D4" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="180"/>
+      <c r="E4" s="146"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="174" t="s">
+      <c r="B5" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="181"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="147"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="179" t="s">
+      <c r="A6" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="170" t="s">
+      <c r="B6" s="136" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="170"/>
-      <c r="D6" s="171" t="s">
+      <c r="C6" s="136"/>
+      <c r="D6" s="137" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="181"/>
+      <c r="E6" s="147"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="184"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="149"/>
+      <c r="E7" s="150"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="166" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="135"/>
+      <c r="C9" s="154"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="135"/>
-      <c r="C10" s="135"/>
+      <c r="B10" s="154"/>
+      <c r="C10" s="154"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="135"/>
-      <c r="C11" s="135"/>
+      <c r="B11" s="154"/>
+      <c r="C11" s="154"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="133"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="138" t="s">
+      <c r="A14" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="135"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="135"/>
-      <c r="B15" s="135"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135"/>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="135"/>
-      <c r="B17" s="135"/>
-      <c r="C17" s="135"/>
-      <c r="D17" s="135"/>
-      <c r="E17" s="135"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2171,10 +2182,10 @@
       <c r="E36" s="66"/>
     </row>
     <row r="37" spans="1:8" s="36" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="139" t="s">
+      <c r="A37" s="168" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="137"/>
+      <c r="B37" s="157"/>
       <c r="C37" s="55"/>
       <c r="D37" s="126">
         <v>87562.7</v>
@@ -2182,10 +2193,10 @@
       <c r="E37" s="106"/>
     </row>
     <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="139" t="s">
+      <c r="A38" s="168" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="137"/>
+      <c r="B38" s="157"/>
       <c r="C38" s="55"/>
       <c r="D38" s="127">
         <v>6646.91</v>
@@ -2355,10 +2366,10 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="166" t="s">
+      <c r="A51" s="171" t="s">
         <v>162</v>
       </c>
-      <c r="B51" s="167"/>
+      <c r="B51" s="172"/>
       <c r="C51" s="5"/>
       <c r="D51" s="127">
         <v>135000</v>
@@ -2407,10 +2418,10 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="140" t="s">
+      <c r="A55" s="169" t="s">
         <v>156</v>
       </c>
-      <c r="B55" s="141"/>
+      <c r="B55" s="170"/>
       <c r="C55" s="5"/>
       <c r="D55" s="127">
         <v>500000</v>
@@ -2418,12 +2429,12 @@
       <c r="E55" s="90"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="136" t="s">
+      <c r="A56" s="156" t="s">
         <v>143</v>
       </c>
-      <c r="B56" s="137"/>
+      <c r="B56" s="157"/>
       <c r="C56" s="56"/>
-      <c r="D56" s="187">
+      <c r="D56" s="152">
         <v>67030</v>
       </c>
       <c r="E56" s="108" t="s">
@@ -2570,26 +2581,26 @@
       <c r="E71" s="103"/>
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="136" t="s">
+      <c r="A72" s="156" t="s">
         <v>167</v>
       </c>
-      <c r="B72" s="144"/>
+      <c r="B72" s="158"/>
       <c r="C72" s="5"/>
-      <c r="D72" s="148">
+      <c r="D72" s="162">
         <v>181000</v>
       </c>
-      <c r="E72" s="150"/>
+      <c r="E72" s="164"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="145"/>
-      <c r="B73" s="146"/>
+      <c r="A73" s="159"/>
+      <c r="B73" s="160"/>
       <c r="C73" s="53"/>
-      <c r="D73" s="186"/>
-      <c r="E73" s="149"/>
+      <c r="D73" s="163"/>
+      <c r="E73" s="165"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="136"/>
-      <c r="B74" s="137"/>
+      <c r="A74" s="156"/>
+      <c r="B74" s="157"/>
       <c r="C74" s="53"/>
       <c r="D74" s="34"/>
       <c r="E74" s="131"/>
@@ -2667,25 +2678,25 @@
     <row r="85" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="142"/>
-      <c r="B87" s="135"/>
-      <c r="C87" s="135"/>
-      <c r="D87" s="135"/>
-      <c r="E87" s="135"/>
+      <c r="A87" s="153"/>
+      <c r="B87" s="154"/>
+      <c r="C87" s="154"/>
+      <c r="D87" s="154"/>
+      <c r="E87" s="154"/>
     </row>
     <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="135"/>
-      <c r="B88" s="135"/>
-      <c r="C88" s="135"/>
-      <c r="D88" s="135"/>
-      <c r="E88" s="135"/>
+      <c r="A88" s="154"/>
+      <c r="B88" s="154"/>
+      <c r="C88" s="154"/>
+      <c r="D88" s="154"/>
+      <c r="E88" s="154"/>
     </row>
     <row r="89" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="135"/>
-      <c r="B89" s="135"/>
-      <c r="C89" s="135"/>
-      <c r="D89" s="135"/>
-      <c r="E89" s="135"/>
+      <c r="A89" s="154"/>
+      <c r="B89" s="154"/>
+      <c r="C89" s="154"/>
+      <c r="D89" s="154"/>
+      <c r="E89" s="154"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
@@ -2721,7 +2732,7 @@
       <c r="C94" s="17"/>
     </row>
     <row r="95" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="185" t="s">
+      <c r="A95" s="151" t="s">
         <v>166</v>
       </c>
       <c r="B95" s="47">
@@ -2840,16 +2851,16 @@
     <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="110" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="143" t="s">
+      <c r="A111" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="B111" s="135"/>
-      <c r="C111" s="135"/>
+      <c r="B111" s="154"/>
+      <c r="C111" s="154"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="135"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="135"/>
+      <c r="A112" s="154"/>
+      <c r="B112" s="154"/>
+      <c r="C112" s="154"/>
     </row>
     <row r="113" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="55" t="s">
@@ -2881,35 +2892,42 @@
       <c r="M116" s="8"/>
     </row>
     <row r="117" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="147"/>
-      <c r="B117" s="135"/>
-      <c r="C117" s="135"/>
-      <c r="D117" s="135"/>
-      <c r="E117" s="135"/>
+      <c r="A117" s="161"/>
+      <c r="B117" s="154"/>
+      <c r="C117" s="154"/>
+      <c r="D117" s="154"/>
+      <c r="E117" s="154"/>
     </row>
     <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="135"/>
-      <c r="B118" s="135"/>
-      <c r="C118" s="135"/>
-      <c r="D118" s="135"/>
-      <c r="E118" s="135"/>
+      <c r="A118" s="154"/>
+      <c r="B118" s="154"/>
+      <c r="C118" s="154"/>
+      <c r="D118" s="154"/>
+      <c r="E118" s="154"/>
     </row>
     <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="135"/>
-      <c r="B119" s="135"/>
-      <c r="C119" s="135"/>
-      <c r="D119" s="135"/>
-      <c r="E119" s="135"/>
+      <c r="A119" s="154"/>
+      <c r="B119" s="154"/>
+      <c r="C119" s="154"/>
+      <c r="D119" s="154"/>
+      <c r="E119" s="154"/>
     </row>
     <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="135"/>
-      <c r="B120" s="135"/>
-      <c r="C120" s="135"/>
-      <c r="D120" s="135"/>
-      <c r="E120" s="135"/>
+      <c r="A120" s="154"/>
+      <c r="B120" s="154"/>
+      <c r="C120" s="154"/>
+      <c r="D120" s="154"/>
+      <c r="E120" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A87:E89"/>
     <mergeCell ref="A111:C112"/>
     <mergeCell ref="A74:B74"/>
@@ -2917,13 +2935,6 @@
     <mergeCell ref="A117:E120"/>
     <mergeCell ref="D72:D73"/>
     <mergeCell ref="E72:E73"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A51:B51"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2965,18 +2976,18 @@
         <v>60</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="155" t="s">
+      <c r="F1" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="154"/>
+      <c r="K1" s="154"/>
+      <c r="L1" s="154"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="154"/>
+      <c r="O1" s="154"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2999,11 +3010,11 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="160">
+      <c r="O2" s="179">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="135"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3025,59 +3036,59 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="164">
+      <c r="O3" s="183">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="165"/>
+      <c r="P3" s="184"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="161" t="s">
+      <c r="B4" s="180" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="151" t="s">
+      <c r="C4" s="175" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="151" t="s">
+      <c r="D4" s="175" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="153" t="s">
+      <c r="E4" s="176" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="151" t="s">
+      <c r="F4" s="175" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="151" t="s">
+      <c r="G4" s="175" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="151" t="s">
+      <c r="H4" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="I4" s="153" t="s">
+      <c r="I4" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="156" t="s">
+      <c r="J4" s="186" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="159" t="s">
+      <c r="K4" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="157" t="s">
+      <c r="L4" s="187" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="159" t="s">
+      <c r="M4" s="178" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="159" t="s">
+      <c r="N4" s="178" t="s">
         <v>78</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="163" t="s">
+      <c r="P4" s="182" t="s">
         <v>80</v>
       </c>
       <c r="S4" s="43"/>
@@ -3086,25 +3097,25 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="152"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
+      <c r="A5" s="174"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="177"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="152"/>
+      <c r="P5" s="174"/>
     </row>
     <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3125,7 +3136,7 @@
       <c r="F6" s="68">
         <v>3</v>
       </c>
-      <c r="G6" s="168">
+      <c r="G6" s="134">
         <v>95430.1</v>
       </c>
       <c r="H6" s="130">
@@ -3188,7 +3199,7 @@
       <c r="F7" s="68">
         <v>3.8</v>
       </c>
-      <c r="G7" s="168">
+      <c r="G7" s="134">
         <v>117849.2</v>
       </c>
       <c r="H7" s="130">
@@ -3249,7 +3260,7 @@
       <c r="F8" s="68">
         <v>3</v>
       </c>
-      <c r="G8" s="168">
+      <c r="G8" s="134">
         <v>98293.3</v>
       </c>
       <c r="H8" s="130">
@@ -3309,7 +3320,7 @@
       <c r="F9" s="68">
         <v>3.1</v>
       </c>
-      <c r="G9" s="168">
+      <c r="G9" s="134">
         <v>270048.03999999998</v>
       </c>
       <c r="H9" s="130">
@@ -3370,7 +3381,7 @@
       <c r="F10" s="68">
         <v>3.1</v>
       </c>
-      <c r="G10" s="168">
+      <c r="G10" s="134">
         <v>98611.5</v>
       </c>
       <c r="H10" s="130"/>
@@ -3426,7 +3437,7 @@
       <c r="F11" s="68">
         <v>3.2</v>
       </c>
-      <c r="G11" s="168">
+      <c r="G11" s="134">
         <v>101792.6</v>
       </c>
       <c r="H11" s="130">
@@ -3486,7 +3497,7 @@
       <c r="F12" s="68">
         <v>3.3</v>
       </c>
-      <c r="G12" s="168">
+      <c r="G12" s="134">
         <v>102343.7</v>
       </c>
       <c r="H12" s="130">
@@ -3546,7 +3557,7 @@
       <c r="F13" s="68">
         <v>6.3</v>
       </c>
-      <c r="G13" s="168">
+      <c r="G13" s="134">
         <v>200403.23</v>
       </c>
       <c r="H13" s="69">
@@ -3608,7 +3619,7 @@
       <c r="F14" s="68">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G14" s="168">
+      <c r="G14" s="134">
         <v>162231.22</v>
       </c>
       <c r="H14" s="69">
@@ -3666,7 +3677,7 @@
       <c r="F15" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G15" s="168">
+      <c r="G15" s="134">
         <v>264918.21000000002</v>
       </c>
       <c r="H15" s="69">
@@ -3726,7 +3737,7 @@
       <c r="F16" s="68">
         <v>6.1</v>
       </c>
-      <c r="G16" s="168">
+      <c r="G16" s="134">
         <v>194041.14</v>
       </c>
       <c r="H16" s="69">
@@ -3784,7 +3795,7 @@
       <c r="F17" s="68">
         <v>5</v>
       </c>
-      <c r="G17" s="168">
+      <c r="G17" s="134">
         <v>155065.13</v>
       </c>
       <c r="H17" s="69">
@@ -3843,7 +3854,7 @@
       <c r="F18" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G18" s="168">
+      <c r="G18" s="134">
         <v>14360927.119999999</v>
       </c>
       <c r="H18" s="69">
@@ -3900,7 +3911,7 @@
       <c r="F19" s="68">
         <v>6.1</v>
       </c>
-      <c r="G19" s="168">
+      <c r="G19" s="134">
         <v>10194042.17</v>
       </c>
       <c r="H19" s="69"/>
@@ -3957,7 +3968,7 @@
       <c r="F20" s="68">
         <v>5</v>
       </c>
-      <c r="G20" s="169">
+      <c r="G20" s="135">
         <v>168321.16</v>
       </c>
       <c r="H20" s="69">
@@ -4018,7 +4029,7 @@
       <c r="F21" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G21" s="168">
+      <c r="G21" s="134">
         <v>264918.15000000002</v>
       </c>
       <c r="H21" s="69">
@@ -4076,7 +4087,7 @@
       <c r="F22" s="68">
         <v>6.1</v>
       </c>
-      <c r="G22" s="169">
+      <c r="G22" s="135">
         <v>194041.2</v>
       </c>
       <c r="H22" s="69">
@@ -4139,7 +4150,7 @@
       <c r="F23" s="68">
         <v>5</v>
       </c>
-      <c r="G23" s="168">
+      <c r="G23" s="134">
         <v>159050.19</v>
       </c>
       <c r="H23" s="69"/>
@@ -4187,14 +4198,14 @@
       <c r="C24" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="62" t="s">
+      <c r="D24" s="188" t="s">
         <v>140</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G24" s="168">
+      <c r="G24" s="134">
         <v>260842.18</v>
       </c>
       <c r="H24" s="69">
@@ -4288,93 +4299,96 @@
     <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
+      <c r="R26" s="189" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="147" t="s">
+      <c r="D28" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="135"/>
-      <c r="H28" s="135"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="135"/>
-      <c r="L28" s="135"/>
-      <c r="M28" s="135"/>
-      <c r="N28" s="135"/>
-      <c r="O28" s="135"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="135"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="135"/>
-      <c r="H29" s="135"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="135"/>
-      <c r="K29" s="135"/>
-      <c r="L29" s="135"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="135"/>
-      <c r="O29" s="135"/>
+      <c r="D29" s="154"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="154"/>
+      <c r="G29" s="154"/>
+      <c r="H29" s="154"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="154"/>
+      <c r="O29" s="154"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
-      <c r="H30" s="135"/>
-      <c r="I30" s="135"/>
-      <c r="J30" s="135"/>
-      <c r="K30" s="135"/>
-      <c r="L30" s="135"/>
-      <c r="M30" s="135"/>
-      <c r="N30" s="135"/>
-      <c r="O30" s="135"/>
+      <c r="D30" s="154"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="154"/>
+      <c r="H30" s="154"/>
+      <c r="I30" s="154"/>
+      <c r="J30" s="154"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="154"/>
+      <c r="N30" s="154"/>
+      <c r="O30" s="154"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="135"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="135"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="135"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="135"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="135"/>
-      <c r="E32" s="135"/>
-      <c r="F32" s="135"/>
-      <c r="G32" s="135"/>
-      <c r="H32" s="135"/>
-      <c r="I32" s="135"/>
-      <c r="J32" s="135"/>
-      <c r="K32" s="135"/>
-      <c r="L32" s="135"/>
-      <c r="M32" s="135"/>
-      <c r="N32" s="135"/>
-      <c r="O32" s="135"/>
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="F32" s="154"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="154"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="154"/>
+      <c r="M32" s="154"/>
+      <c r="N32" s="154"/>
+      <c r="O32" s="154"/>
     </row>
     <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="135"/>
-      <c r="H33" s="135"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="135"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="135"/>
-      <c r="M33" s="135"/>
-      <c r="N33" s="135"/>
-      <c r="O33" s="135"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="154"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="154"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
@@ -4382,6 +4396,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4394,13 +4415,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
